--- a/restaurant_crawler/list/總表.xlsx
+++ b/restaurant_crawler/list/總表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\slow3\OneDrive\桌面\GitHubProjects\BYOB\restaurant_crawler\list\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF51C90B-E4D4-4393-B62E-51D583DE4AEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{476AEC7E-633F-4189-B565-157ABEEF89F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{E8354C52-640D-495B-A68D-B024E43CC161}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="807" uniqueCount="539">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1110" uniqueCount="741">
   <si>
     <t>name</t>
   </si>
@@ -1668,6 +1668,616 @@
   </si>
   <si>
     <t>floral23250990@yahoo.com.tw</t>
+  </si>
+  <si>
+    <t>A.K.12 美式小館-漢堡、義大利麵、飲料暢飲、毛孩餐點</t>
+  </si>
+  <si>
+    <t>Oldies Burger 歐帝斯美墨餐廳</t>
+  </si>
+  <si>
+    <t>復古豪斯Retro House</t>
+  </si>
+  <si>
+    <t>Nola Kitchen 台北林森店(二號巷子口內、喜來登飯店後方)</t>
+  </si>
+  <si>
+    <t>Selfish Burger自私漢堡</t>
+  </si>
+  <si>
+    <t>爸爸Kevin美食BBQ</t>
+  </si>
+  <si>
+    <t>莫克漢堡（致遠店）Moke'sburger 石牌手拍牛肉美式漢堡</t>
+  </si>
+  <si>
+    <t>ED's Diner美式BBQ燒烤餐館 Est. 2011</t>
+  </si>
+  <si>
+    <t>AN-Burger</t>
+  </si>
+  <si>
+    <t>The Corner Pit 角窩美式餐酒館</t>
+  </si>
+  <si>
+    <t>Fa Burger</t>
+  </si>
+  <si>
+    <t>小南港-懶人私廚</t>
+  </si>
+  <si>
+    <t>KGB Kiwi Gourmet Burgers</t>
+  </si>
+  <si>
+    <t>SKRABUR 黑膠漢堡</t>
+  </si>
+  <si>
+    <t>和牛漢堡</t>
+  </si>
+  <si>
+    <t>SALT&amp;STONE 台北101餐廳</t>
+  </si>
+  <si>
+    <t>Housebistro好適廚坊</t>
+  </si>
+  <si>
+    <t>Takeout Burger&amp;Cafe 延吉店 （最後點餐21：30）/美式漢堡/寵物友善/大安區美食/貓咪餐廳</t>
+  </si>
+  <si>
+    <t>Omnivore</t>
+  </si>
+  <si>
+    <t>凱莉餐廳</t>
+  </si>
+  <si>
+    <t>JB's Diner</t>
+  </si>
+  <si>
+    <t>VASA 瓦薩美式餐廳 - 內科門市</t>
+  </si>
+  <si>
+    <t>老倉庫</t>
+  </si>
+  <si>
+    <t>小倉庫食研所</t>
+  </si>
+  <si>
+    <t>2015ak12@gmail.com</t>
+  </si>
+  <si>
+    <t>oldiesburger2020@gmail.com</t>
+  </si>
+  <si>
+    <t>retrohouse551@gmail.com</t>
+  </si>
+  <si>
+    <t>nolakitchentw@gmail.com</t>
+  </si>
+  <si>
+    <t>sb001@sunspark-group.com</t>
+  </si>
+  <si>
+    <t>eat@88k.com.tw</t>
+  </si>
+  <si>
+    <t>jeffliu86028@gmail.com</t>
+  </si>
+  <si>
+    <t>edsdinertaipei@gmail.com</t>
+  </si>
+  <si>
+    <t>anburger21002862@gmail.com</t>
+  </si>
+  <si>
+    <t>tcp87868858@gmail.com</t>
+  </si>
+  <si>
+    <t>fa.burgerr@gmail.com</t>
+  </si>
+  <si>
+    <t>littlenk88@gmail.com</t>
+  </si>
+  <si>
+    <t>kgbtaiwan@gmail.com</t>
+  </si>
+  <si>
+    <t>clancy0430@gmail.com</t>
+  </si>
+  <si>
+    <t>burgerversetw@gmail.com</t>
+  </si>
+  <si>
+    <t>sweetservice@womany.net</t>
+  </si>
+  <si>
+    <t>housebistro367@gmail.com</t>
+  </si>
+  <si>
+    <t>mars0727@hotmail.com</t>
+  </si>
+  <si>
+    <t>omnivore.taiwan@gmail.com</t>
+  </si>
+  <si>
+    <t>americanvillagetaipei@gmail.com</t>
+  </si>
+  <si>
+    <t>badge_check@3x.png</t>
+  </si>
+  <si>
+    <t>vasaservice@sunspark-group.com</t>
+  </si>
+  <si>
+    <t>marcus722@gmail.com</t>
+  </si>
+  <si>
+    <t>marcus77083798@gmail.com</t>
+  </si>
+  <si>
+    <t>美式餐廳</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>角落utopia</t>
+  </si>
+  <si>
+    <t>草根早午餐 TOUCH WOOD</t>
+  </si>
+  <si>
+    <t>倆人初餐</t>
+  </si>
+  <si>
+    <t>花嘴廚房</t>
+  </si>
+  <si>
+    <t>bliss4758@gmail.com</t>
+  </si>
+  <si>
+    <t>touchwood0527@gmail.com</t>
+  </si>
+  <si>
+    <t>monster02212002@gmail.com</t>
+  </si>
+  <si>
+    <t>sirion1024@yahoo.com.tw</t>
+  </si>
+  <si>
+    <t>badge_healthy@3x.png</t>
+  </si>
+  <si>
+    <t>曼谷泰式料理（永和店）</t>
+  </si>
+  <si>
+    <t>哈泰 泰式料理餐廳 Hot Thai Thai Cuisine</t>
+  </si>
+  <si>
+    <t>頌丹樂 泰式伊善料理</t>
+  </si>
+  <si>
+    <t>香米泰國料理{大直忠泰店}</t>
+  </si>
+  <si>
+    <t>心泰原創泰國料理-敦南店</t>
+  </si>
+  <si>
+    <t>香茅廚泰式餐廳微風復興店Chef Lemongrass Thai Bistro</t>
+  </si>
+  <si>
+    <t>泰美</t>
+  </si>
+  <si>
+    <t>椰兄泰式料理餐廳 中山店</t>
+  </si>
+  <si>
+    <t>小食泰泰式料理餐廳/會議便當/午餐/Fanthaisy Thai Restaurants/聚餐/好吃便當/外送便當/晚餐/台北美食/外送便當/客製便當/附近美食</t>
+  </si>
+  <si>
+    <t>Lisa泰式美食</t>
+  </si>
+  <si>
+    <t>泰好吃泰國船麵</t>
+  </si>
+  <si>
+    <t>Zaaptaipei</t>
+  </si>
+  <si>
+    <t>東輝韓食館</t>
+  </si>
+  <si>
+    <t>這味泰泰Mrs. Thai Thai-忠孝SOGO店</t>
+  </si>
+  <si>
+    <t>台北泰 民生店</t>
+  </si>
+  <si>
+    <t>打拋飯泰味專賣店 | 泰式便當外送</t>
+  </si>
+  <si>
+    <t>食尚曼谷</t>
+  </si>
+  <si>
+    <t>韓味道--道地炸雞 韓式韓國料理餐廳</t>
+  </si>
+  <si>
+    <t>新泰村 泰式小吃</t>
+  </si>
+  <si>
+    <t>Nim's 泰式廚房 (担担泰)</t>
+  </si>
+  <si>
+    <t>Thai Hao老麵攤 - 光復店｜傳承自Kanokwan 的好味道</t>
+  </si>
+  <si>
+    <t>泰滾 Rolling Thai 泰式火鍋(南京店）</t>
+  </si>
+  <si>
+    <t>betty840810@gmail.com</t>
+  </si>
+  <si>
+    <t>lisaliu0811@yahoo.com.tw</t>
+  </si>
+  <si>
+    <t>logo@2x.png</t>
+  </si>
+  <si>
+    <t>homesthai@gmail.com</t>
+  </si>
+  <si>
+    <t>service@spoon.com.tw</t>
+  </si>
+  <si>
+    <t>chef0266003210@gmail.com</t>
+  </si>
+  <si>
+    <t>thaimade@yahoo.com.tw</t>
+  </si>
+  <si>
+    <t>icon_ig_450x264_72fad095-eef9-4f70-bf48-7f1908bee838_480x480@2x.png</t>
+  </si>
+  <si>
+    <t>service@steamage.com</t>
+  </si>
+  <si>
+    <t>abc0989772284@gamil.com</t>
+  </si>
+  <si>
+    <t>peter0920@yahoo.com.tw</t>
+  </si>
+  <si>
+    <t>zaaptaipei@gmail.com</t>
+  </si>
+  <si>
+    <t>camjatang@gmail.com</t>
+  </si>
+  <si>
+    <t>mrs.thai.taiwan@gmail.com</t>
+  </si>
+  <si>
+    <t>taipei.thai.yunnan.thai@gmail.com</t>
+  </si>
+  <si>
+    <t>jain.ting@gmail.com</t>
+  </si>
+  <si>
+    <t>fsbk40@gmail.com</t>
+  </si>
+  <si>
+    <t>jason180cm@gmial.com</t>
+  </si>
+  <si>
+    <t>tuang_yui@hotmail.com</t>
+  </si>
+  <si>
+    <t>yeh.chris@msa.hinet.net</t>
+  </si>
+  <si>
+    <t>n91m001@gmail.com</t>
+  </si>
+  <si>
+    <t>square@gmail.com</t>
+  </si>
+  <si>
+    <t>泰式料理 韓式料理</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>泰食館 Luv2eat THAI</t>
+  </si>
+  <si>
+    <t>安泰泰式料理</t>
+  </si>
+  <si>
+    <t>海雲韓式料理｜新莊店</t>
+  </si>
+  <si>
+    <t>我不怕你泰胖</t>
+  </si>
+  <si>
+    <t>大杵臼 ส้มตําครกยักษ์</t>
+  </si>
+  <si>
+    <t>新山韓國烤肉</t>
+  </si>
+  <si>
+    <t>m66chengwei@yahoo.com.tw</t>
+  </si>
+  <si>
+    <t>3_2fb73e53-b0bc-4054-9602-5c2f09fbef25_480x480@2x.png</t>
+  </si>
+  <si>
+    <t>a0970210668@gmail.com</t>
+  </si>
+  <si>
+    <t>haiyun.korea@gmail.com</t>
+  </si>
+  <si>
+    <t>cougar741004@hotmail.com</t>
+  </si>
+  <si>
+    <t>suchada.sithiwong@gmail.com</t>
+  </si>
+  <si>
+    <t>rollingthaitw@gmail.com</t>
+  </si>
+  <si>
+    <t>xinshanbulgogi@gmail.com</t>
+  </si>
+  <si>
+    <t>Salon et Tutu 酴塗小酒館</t>
+  </si>
+  <si>
+    <t>醉好 Another Round</t>
+  </si>
+  <si>
+    <t>UFO Nocturnal Shisha 餐酒館 - 酒吧</t>
+  </si>
+  <si>
+    <t>The Misanthrope Society 厭世會社 😞 Cafe Bistro with Books &amp; Arts</t>
+  </si>
+  <si>
+    <t>My Other Place Restaurant &amp; Bar 我的家餐廳餐酒館｜台北松山區美式中式料理｜音樂酒館・運動酒吧推薦｜近南京復興／忠孝復興／小巨蛋站｜東區聚餐首選</t>
+  </si>
+  <si>
+    <t>A Train Leads The Way To Jazz</t>
+  </si>
+  <si>
+    <t>Plan B 歐陸街頭市集咖啡｜台北東區忠孝敦化咖啡推薦｜台北寵物友善｜台北生日包場｜台北大安區餐廳包廂｜公司聚餐推薦</t>
+  </si>
+  <si>
+    <t>STEP ONE TAIPEI ｜駐唱｜餐酒｜水煙｜酒吧｜</t>
+  </si>
+  <si>
+    <t>酒等了・ 臺北流行音樂中心 Taipei Music Center</t>
+  </si>
+  <si>
+    <t>Nowhere Taipei 墨西哥餐酒館 | PUB</t>
+  </si>
+  <si>
+    <t>salonettutu@gmail.com</t>
+  </si>
+  <si>
+    <t>customercare@magipea.com</t>
+  </si>
+  <si>
+    <t>nocturnalufo30@gmail.com</t>
+  </si>
+  <si>
+    <t>projectlee.jimmy@gmail.com</t>
+  </si>
+  <si>
+    <t>ian_lin_3@hotmail.com</t>
+  </si>
+  <si>
+    <t>wuchenghen@hotmail.com</t>
+  </si>
+  <si>
+    <t>ssur.cc@gmail.com</t>
+  </si>
+  <si>
+    <t>service@wait9time.com</t>
+  </si>
+  <si>
+    <t>nowheretaipei2024@gmail.com</t>
+  </si>
+  <si>
+    <t>小酒館 Bistro</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AWT Bistro下班後餐酒館</t>
+  </si>
+  <si>
+    <t>ALLEZ BISTRO來酒館（餐酒館）</t>
+  </si>
+  <si>
+    <t>The Scent Pasta House Since 2012/2025全新改裝&amp;菜單/Happy Hours</t>
+  </si>
+  <si>
+    <t>防空洞｜庇護所-Bar</t>
+  </si>
+  <si>
+    <t>你覺得呢餐酒館</t>
+  </si>
+  <si>
+    <t>叁外 Bistro (小酒館)</t>
+  </si>
+  <si>
+    <t>去憂餐酒館 Chill Bistro &amp; Bar</t>
+  </si>
+  <si>
+    <t>Bistro O 避世所</t>
+  </si>
+  <si>
+    <t>Cie Cie Taipei</t>
+  </si>
+  <si>
+    <t>安慰劑 Placebo Taipei</t>
+  </si>
+  <si>
+    <t>瑪德蓮小酒館</t>
+  </si>
+  <si>
+    <t>酒咖飲冰室 JIU KA Bistro &amp; Bar</t>
+  </si>
+  <si>
+    <t>JupJup 精釀生啤餐酒館</t>
+  </si>
+  <si>
+    <t>89 Loop Sports Bar</t>
+  </si>
+  <si>
+    <t>動物園早午餐酒館 Zoo bistro &amp; brunch｜</t>
+  </si>
+  <si>
+    <t>覓‘s咖啡小酒館 Miss Coffee Bar</t>
+  </si>
+  <si>
+    <t>摩德年代繆斯餐酒館</t>
+  </si>
+  <si>
+    <t>takeoffice2018@gmail.com</t>
+  </si>
+  <si>
+    <t>jazrael.w@gmail.com</t>
+  </si>
+  <si>
+    <t>allezbistro@gmail.com</t>
+  </si>
+  <si>
+    <t>xmezquita@gmail.com</t>
+  </si>
+  <si>
+    <t>barshelter888@gmail.com</t>
+  </si>
+  <si>
+    <t>whatdoyouthink26045@gmail.com</t>
+  </si>
+  <si>
+    <t>shanwai3737@gmail.com</t>
+  </si>
+  <si>
+    <t>yardezmu@gmail.com</t>
+  </si>
+  <si>
+    <t>bistroobistro@gmail.com</t>
+  </si>
+  <si>
+    <t>cs@myfunnow.com</t>
+  </si>
+  <si>
+    <t>ciecietaipei@gmail.com</t>
+  </si>
+  <si>
+    <t>placebobar@gmail.com</t>
+  </si>
+  <si>
+    <t>bistromadeleine192@gmail.com</t>
+  </si>
+  <si>
+    <t>supreme1983@hotmail.com</t>
+  </si>
+  <si>
+    <t>japjapbikini@gmail.com</t>
+  </si>
+  <si>
+    <t>89loopsportsbar@gmail.com</t>
+  </si>
+  <si>
+    <t>jobe.bistro@gmail.com</t>
+  </si>
+  <si>
+    <t>ivyivy1129@gmail.com</t>
+  </si>
+  <si>
+    <t>modism.cafe@gmail.com</t>
+  </si>
+  <si>
+    <t>帝王食補 世貿店</t>
+  </si>
+  <si>
+    <t>阿和師薑母鴨</t>
+  </si>
+  <si>
+    <t>大食神炭燒薑母鴨</t>
+  </si>
+  <si>
+    <t>下港吔羊肉專賣店</t>
+  </si>
+  <si>
+    <t>霸味薑母鴨-內湖旗艦店</t>
+  </si>
+  <si>
+    <t>榮星羊雞城-冷凍羊肉爐宅配 台北美食 台北火鍋 台北羊肉爐 台北餐廳 台北割菜雞</t>
+  </si>
+  <si>
+    <t>義村羊肉爐</t>
+  </si>
+  <si>
+    <t>長疆碳燒羊肉爐-北投店</t>
+  </si>
+  <si>
+    <t>霸味薑母鴨</t>
+  </si>
+  <si>
+    <t>新店霸味薑母鴨</t>
+  </si>
+  <si>
+    <t>山羊城 全羊館 羊肉爐 (總店)重陽店</t>
+  </si>
+  <si>
+    <t>泉記老鍋鋪 麻辣鍋</t>
+  </si>
+  <si>
+    <t>紅蕃薑母鴨</t>
+  </si>
+  <si>
+    <t>老主顧紅蟳薑母鴨總店</t>
+  </si>
+  <si>
+    <t>tain21083@gmail.com</t>
+  </si>
+  <si>
+    <t>angelplay77@gmail.com</t>
+  </si>
+  <si>
+    <t>jacky19960713@gmail.com</t>
+  </si>
+  <si>
+    <t>solotankeq@gmail.com</t>
+  </si>
+  <si>
+    <t>tw0928005899@yahoo.com.tw</t>
+  </si>
+  <si>
+    <t>jimmy.tpe@gmail.com</t>
+  </si>
+  <si>
+    <t>b0920004682@gmail.com</t>
+  </si>
+  <si>
+    <t>h0968131323@yahoo.com.tw</t>
+  </si>
+  <si>
+    <t>wow559899@gmail.com</t>
+  </si>
+  <si>
+    <t>atm666666@yahoo.com.tw</t>
+  </si>
+  <si>
+    <t>info@goat-town.com</t>
+  </si>
+  <si>
+    <t>dkny0933045111@gmail.com</t>
+  </si>
+  <si>
+    <t>starismylove98@gmail.com</t>
+  </si>
+  <si>
+    <t>poppy1688@yahoo.com.tw</t>
+  </si>
+  <si>
+    <t>火鍋 羊肉爐 薑母鴨</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1757,7 +2367,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1772,13 +2382,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -2121,11 +2724,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDC20CA0-404E-4459-AB09-3585D9067841}">
-  <dimension ref="A1:H281"/>
+  <dimension ref="A1:H373"/>
   <sheetFormatPr defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="43.77734375" style="2" customWidth="1"/>
-    <col min="2" max="2" width="33.33203125" style="8" customWidth="1"/>
+    <col min="2" max="2" width="33.33203125" style="2" customWidth="1"/>
     <col min="3" max="3" width="18.88671875" style="2" customWidth="1"/>
     <col min="4" max="7" width="8.88671875" style="2"/>
     <col min="8" max="8" width="20.88671875" style="2" customWidth="1"/>
@@ -2136,7 +2739,7 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
@@ -2153,7 +2756,7 @@
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="5" t="s">
         <v>23</v>
       </c>
       <c r="C2" s="4" t="s">
@@ -2167,7 +2770,7 @@
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C3" s="4" t="s">
@@ -2181,7 +2784,7 @@
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C4" s="4" t="s">
@@ -2195,7 +2798,7 @@
       <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="5" t="s">
         <v>26</v>
       </c>
       <c r="C5" s="4" t="s">
@@ -2212,7 +2815,7 @@
       <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="5" t="s">
         <v>27</v>
       </c>
       <c r="C6" s="4" t="s">
@@ -2226,7 +2829,7 @@
       <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C7" s="4" t="s">
@@ -2240,7 +2843,7 @@
       <c r="A8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C8" s="4" t="s">
@@ -2254,7 +2857,7 @@
       <c r="A9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="5" t="s">
         <v>30</v>
       </c>
       <c r="C9" s="4" t="s">
@@ -2268,7 +2871,7 @@
       <c r="A10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C10" s="4" t="s">
@@ -2282,7 +2885,7 @@
       <c r="A11" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="5" t="s">
         <v>32</v>
       </c>
       <c r="C11" s="4" t="s">
@@ -2296,7 +2899,7 @@
       <c r="A12" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="5" t="s">
         <v>33</v>
       </c>
       <c r="C12" s="4" t="s">
@@ -2310,7 +2913,7 @@
       <c r="A13" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="5" t="s">
         <v>34</v>
       </c>
       <c r="C13" s="4" t="s">
@@ -2322,7 +2925,7 @@
       <c r="A14" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="5" t="s">
         <v>35</v>
       </c>
       <c r="C14" s="4" t="s">
@@ -2334,7 +2937,7 @@
       <c r="A15" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="5" t="s">
         <v>36</v>
       </c>
       <c r="C15" s="4" t="s">
@@ -2346,7 +2949,7 @@
       <c r="A16" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="5" t="s">
         <v>37</v>
       </c>
       <c r="C16" s="4" t="s">
@@ -2358,7 +2961,7 @@
       <c r="A17" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="5" t="s">
         <v>38</v>
       </c>
       <c r="C17" s="4" t="s">
@@ -2370,7 +2973,7 @@
       <c r="A18" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="5" t="s">
         <v>39</v>
       </c>
       <c r="C18" s="4" t="s">
@@ -2382,7 +2985,7 @@
       <c r="A19" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="5" t="s">
         <v>40</v>
       </c>
       <c r="C19" s="4" t="s">
@@ -2394,7 +2997,7 @@
       <c r="A20" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="5" t="s">
         <v>41</v>
       </c>
       <c r="C20" s="4" t="s">
@@ -2406,7 +3009,7 @@
       <c r="A21" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="B21" s="5" t="s">
         <v>42</v>
       </c>
       <c r="C21" s="4" t="s">
@@ -2418,7 +3021,7 @@
       <c r="A22" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="B22" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C22" s="4" t="s">
@@ -2430,7 +3033,7 @@
       <c r="A23" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B23" s="7" t="s">
+      <c r="B23" s="5" t="s">
         <v>75</v>
       </c>
       <c r="C23" s="2" t="s">
@@ -2442,7 +3045,7 @@
       <c r="A24" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B24" s="7" t="s">
+      <c r="B24" s="5" t="s">
         <v>76</v>
       </c>
       <c r="C24" s="2" t="s">
@@ -2454,7 +3057,7 @@
       <c r="A25" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="B25" s="5" t="s">
         <v>77</v>
       </c>
       <c r="C25" s="2" t="s">
@@ -2466,7 +3069,7 @@
       <c r="A26" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="B26" s="7" t="s">
+      <c r="B26" s="5" t="s">
         <v>78</v>
       </c>
       <c r="C26" s="2" t="s">
@@ -2478,7 +3081,7 @@
       <c r="A27" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B27" s="7" t="s">
+      <c r="B27" s="5" t="s">
         <v>79</v>
       </c>
       <c r="C27" s="2" t="s">
@@ -2490,7 +3093,7 @@
       <c r="A28" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="B28" s="7" t="s">
+      <c r="B28" s="5" t="s">
         <v>80</v>
       </c>
       <c r="C28" s="2" t="s">
@@ -2502,7 +3105,7 @@
       <c r="A29" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="B29" s="7" t="s">
+      <c r="B29" s="5" t="s">
         <v>81</v>
       </c>
       <c r="C29" s="2" t="s">
@@ -2514,7 +3117,7 @@
       <c r="A30" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="B30" s="7" t="s">
+      <c r="B30" s="5" t="s">
         <v>82</v>
       </c>
       <c r="C30" s="2" t="s">
@@ -2526,7 +3129,7 @@
       <c r="A31" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B31" s="7" t="s">
+      <c r="B31" s="5" t="s">
         <v>83</v>
       </c>
       <c r="C31" s="2" t="s">
@@ -2538,7 +3141,7 @@
       <c r="A32" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="B32" s="7" t="s">
+      <c r="B32" s="5" t="s">
         <v>84</v>
       </c>
       <c r="C32" s="2" t="s">
@@ -2550,7 +3153,7 @@
       <c r="A33" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="7" t="s">
+      <c r="B33" s="5" t="s">
         <v>85</v>
       </c>
       <c r="C33" s="2" t="s">
@@ -2562,7 +3165,7 @@
       <c r="A34" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="B34" s="7" t="s">
+      <c r="B34" s="5" t="s">
         <v>86</v>
       </c>
       <c r="C34" s="2" t="s">
@@ -2574,7 +3177,7 @@
       <c r="A35" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="B35" s="7" t="s">
+      <c r="B35" s="5" t="s">
         <v>87</v>
       </c>
       <c r="C35" s="2" t="s">
@@ -2586,7 +3189,7 @@
       <c r="A36" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="B36" s="7" t="s">
+      <c r="B36" s="5" t="s">
         <v>88</v>
       </c>
       <c r="C36" s="2" t="s">
@@ -2598,7 +3201,7 @@
       <c r="A37" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="B37" s="7" t="s">
+      <c r="B37" s="5" t="s">
         <v>89</v>
       </c>
       <c r="C37" s="2" t="s">
@@ -2610,7 +3213,7 @@
       <c r="A38" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B38" s="7" t="s">
+      <c r="B38" s="5" t="s">
         <v>90</v>
       </c>
       <c r="C38" s="2" t="s">
@@ -2622,7 +3225,7 @@
       <c r="A39" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B39" s="7" t="s">
+      <c r="B39" s="5" t="s">
         <v>91</v>
       </c>
       <c r="C39" s="2" t="s">
@@ -2634,7 +3237,7 @@
       <c r="A40" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="B40" s="7" t="s">
+      <c r="B40" s="5" t="s">
         <v>92</v>
       </c>
       <c r="C40" s="2" t="s">
@@ -2646,7 +3249,7 @@
       <c r="A41" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="B41" s="7" t="s">
+      <c r="B41" s="5" t="s">
         <v>93</v>
       </c>
       <c r="C41" s="2" t="s">
@@ -2658,7 +3261,7 @@
       <c r="A42" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B42" s="7" t="s">
+      <c r="B42" s="5" t="s">
         <v>94</v>
       </c>
       <c r="C42" s="2" t="s">
@@ -2670,7 +3273,7 @@
       <c r="A43" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="B43" s="7" t="s">
+      <c r="B43" s="5" t="s">
         <v>95</v>
       </c>
       <c r="C43" s="2" t="s">
@@ -2682,7 +3285,7 @@
       <c r="A44" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="B44" s="7" t="s">
+      <c r="B44" s="5" t="s">
         <v>96</v>
       </c>
       <c r="C44" s="2" t="s">
@@ -2694,7 +3297,7 @@
       <c r="A45" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="B45" s="7" t="s">
+      <c r="B45" s="5" t="s">
         <v>97</v>
       </c>
       <c r="C45" s="2" t="s">
@@ -2706,7 +3309,7 @@
       <c r="A46" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="B46" s="7" t="s">
+      <c r="B46" s="5" t="s">
         <v>98</v>
       </c>
       <c r="C46" s="2" t="s">
@@ -2718,7 +3321,7 @@
       <c r="A47" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="B47" s="7" t="s">
+      <c r="B47" s="5" t="s">
         <v>99</v>
       </c>
       <c r="C47" s="2" t="s">
@@ -2730,7 +3333,7 @@
       <c r="A48" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="B48" s="7" t="s">
+      <c r="B48" s="5" t="s">
         <v>100</v>
       </c>
       <c r="C48" s="2" t="s">
@@ -2742,7 +3345,7 @@
       <c r="A49" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="B49" s="7" t="s">
+      <c r="B49" s="5" t="s">
         <v>101</v>
       </c>
       <c r="C49" s="2" t="s">
@@ -2754,7 +3357,7 @@
       <c r="A50" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="B50" s="7" t="s">
+      <c r="B50" s="5" t="s">
         <v>141</v>
       </c>
       <c r="C50" s="2" t="s">
@@ -2766,7 +3369,7 @@
       <c r="A51" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="B51" s="7" t="s">
+      <c r="B51" s="5" t="s">
         <v>142</v>
       </c>
       <c r="C51" s="2" t="s">
@@ -2778,7 +3381,7 @@
       <c r="A52" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="B52" s="7" t="s">
+      <c r="B52" s="5" t="s">
         <v>143</v>
       </c>
       <c r="C52" s="2" t="s">
@@ -2790,7 +3393,7 @@
       <c r="A53" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="B53" s="7" t="s">
+      <c r="B53" s="5" t="s">
         <v>144</v>
       </c>
       <c r="C53" s="2" t="s">
@@ -2802,7 +3405,7 @@
       <c r="A54" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="B54" s="7" t="s">
+      <c r="B54" s="5" t="s">
         <v>145</v>
       </c>
       <c r="C54" s="2" t="s">
@@ -2814,7 +3417,7 @@
       <c r="A55" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="B55" s="7" t="s">
+      <c r="B55" s="5" t="s">
         <v>146</v>
       </c>
       <c r="C55" s="2" t="s">
@@ -2826,7 +3429,7 @@
       <c r="A56" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="B56" s="7" t="s">
+      <c r="B56" s="5" t="s">
         <v>147</v>
       </c>
       <c r="C56" s="2" t="s">
@@ -2838,7 +3441,7 @@
       <c r="A57" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="B57" s="7" t="s">
+      <c r="B57" s="5" t="s">
         <v>148</v>
       </c>
       <c r="C57" s="2" t="s">
@@ -2850,7 +3453,7 @@
       <c r="A58" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="B58" s="7" t="s">
+      <c r="B58" s="5" t="s">
         <v>149</v>
       </c>
       <c r="C58" s="2" t="s">
@@ -2862,7 +3465,7 @@
       <c r="A59" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="B59" s="7" t="s">
+      <c r="B59" s="5" t="s">
         <v>150</v>
       </c>
       <c r="C59" s="2" t="s">
@@ -2874,7 +3477,7 @@
       <c r="A60" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="B60" s="7" t="s">
+      <c r="B60" s="5" t="s">
         <v>151</v>
       </c>
       <c r="C60" s="2" t="s">
@@ -2886,7 +3489,7 @@
       <c r="A61" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="B61" s="7" t="s">
+      <c r="B61" s="5" t="s">
         <v>152</v>
       </c>
       <c r="C61" s="2" t="s">
@@ -2898,7 +3501,7 @@
       <c r="A62" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="B62" s="7" t="s">
+      <c r="B62" s="5" t="s">
         <v>153</v>
       </c>
       <c r="C62" s="2" t="s">
@@ -2910,7 +3513,7 @@
       <c r="A63" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="B63" s="7" t="s">
+      <c r="B63" s="5" t="s">
         <v>154</v>
       </c>
       <c r="C63" s="2" t="s">
@@ -2922,7 +3525,7 @@
       <c r="A64" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="B64" s="7" t="s">
+      <c r="B64" s="5" t="s">
         <v>155</v>
       </c>
       <c r="C64" s="2" t="s">
@@ -2934,7 +3537,7 @@
       <c r="A65" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="B65" s="7" t="s">
+      <c r="B65" s="5" t="s">
         <v>156</v>
       </c>
       <c r="C65" s="2" t="s">
@@ -2946,7 +3549,7 @@
       <c r="A66" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="B66" s="7" t="s">
+      <c r="B66" s="5" t="s">
         <v>157</v>
       </c>
       <c r="C66" s="2" t="s">
@@ -2958,7 +3561,7 @@
       <c r="A67" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="B67" s="7" t="s">
+      <c r="B67" s="5" t="s">
         <v>158</v>
       </c>
       <c r="C67" s="2" t="s">
@@ -2970,7 +3573,7 @@
       <c r="A68" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="B68" s="7" t="s">
+      <c r="B68" s="5" t="s">
         <v>159</v>
       </c>
       <c r="C68" s="2" t="s">
@@ -2982,7 +3585,7 @@
       <c r="A69" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="B69" s="7" t="s">
+      <c r="B69" s="5" t="s">
         <v>160</v>
       </c>
       <c r="C69" s="2" t="s">
@@ -2994,7 +3597,7 @@
       <c r="A70" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="B70" s="7" t="s">
+      <c r="B70" s="5" t="s">
         <v>161</v>
       </c>
       <c r="C70" s="2" t="s">
@@ -3006,7 +3609,7 @@
       <c r="A71" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="B71" s="7" t="s">
+      <c r="B71" s="5" t="s">
         <v>162</v>
       </c>
       <c r="C71" s="2" t="s">
@@ -3018,7 +3621,7 @@
       <c r="A72" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="B72" s="7" t="s">
+      <c r="B72" s="5" t="s">
         <v>163</v>
       </c>
       <c r="C72" s="2" t="s">
@@ -3030,7 +3633,7 @@
       <c r="A73" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="B73" s="7" t="s">
+      <c r="B73" s="5" t="s">
         <v>164</v>
       </c>
       <c r="C73" s="2" t="s">
@@ -3042,7 +3645,7 @@
       <c r="A74" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="B74" s="7" t="s">
+      <c r="B74" s="5" t="s">
         <v>165</v>
       </c>
       <c r="C74" s="2" t="s">
@@ -3054,7 +3657,7 @@
       <c r="A75" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="B75" s="7" t="s">
+      <c r="B75" s="5" t="s">
         <v>166</v>
       </c>
       <c r="C75" s="2" t="s">
@@ -3066,7 +3669,7 @@
       <c r="A76" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="B76" s="7" t="s">
+      <c r="B76" s="5" t="s">
         <v>167</v>
       </c>
       <c r="C76" s="2" t="s">
@@ -3078,7 +3681,7 @@
       <c r="A77" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="B77" s="7" t="s">
+      <c r="B77" s="5" t="s">
         <v>168</v>
       </c>
       <c r="C77" s="2" t="s">
@@ -3090,7 +3693,7 @@
       <c r="A78" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="B78" s="7" t="s">
+      <c r="B78" s="5" t="s">
         <v>169</v>
       </c>
       <c r="C78" s="2" t="s">
@@ -3102,7 +3705,7 @@
       <c r="A79" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="B79" s="7" t="s">
+      <c r="B79" s="5" t="s">
         <v>170</v>
       </c>
       <c r="C79" s="2" t="s">
@@ -3114,7 +3717,7 @@
       <c r="A80" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="B80" s="7" t="s">
+      <c r="B80" s="5" t="s">
         <v>171</v>
       </c>
       <c r="C80" s="2" t="s">
@@ -3126,7 +3729,7 @@
       <c r="A81" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="B81" s="7" t="s">
+      <c r="B81" s="5" t="s">
         <v>172</v>
       </c>
       <c r="C81" s="2" t="s">
@@ -3138,7 +3741,7 @@
       <c r="A82" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="B82" s="7" t="s">
+      <c r="B82" s="5" t="s">
         <v>173</v>
       </c>
       <c r="C82" s="2" t="s">
@@ -3150,7 +3753,7 @@
       <c r="A83" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="B83" s="7" t="s">
+      <c r="B83" s="5" t="s">
         <v>174</v>
       </c>
       <c r="C83" s="2" t="s">
@@ -3162,7 +3765,7 @@
       <c r="A84" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="B84" s="7" t="s">
+      <c r="B84" s="5" t="s">
         <v>175</v>
       </c>
       <c r="C84" s="2" t="s">
@@ -3174,7 +3777,7 @@
       <c r="A85" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="B85" s="7" t="s">
+      <c r="B85" s="5" t="s">
         <v>176</v>
       </c>
       <c r="C85" s="2" t="s">
@@ -3186,7 +3789,7 @@
       <c r="A86" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="B86" s="7" t="s">
+      <c r="B86" s="5" t="s">
         <v>177</v>
       </c>
       <c r="C86" s="2" t="s">
@@ -3198,7 +3801,7 @@
       <c r="A87" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="B87" s="7" t="s">
+      <c r="B87" s="5" t="s">
         <v>178</v>
       </c>
       <c r="C87" s="2" t="s">
@@ -3210,7 +3813,7 @@
       <c r="A88" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="B88" s="7" t="s">
+      <c r="B88" s="5" t="s">
         <v>198</v>
       </c>
       <c r="C88" s="2" t="s">
@@ -3222,7 +3825,7 @@
       <c r="A89" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="B89" s="7" t="s">
+      <c r="B89" s="5" t="s">
         <v>199</v>
       </c>
       <c r="C89" s="2" t="s">
@@ -3234,7 +3837,7 @@
       <c r="A90" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="B90" s="7" t="s">
+      <c r="B90" s="5" t="s">
         <v>200</v>
       </c>
       <c r="C90" s="2" t="s">
@@ -3246,7 +3849,7 @@
       <c r="A91" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="B91" s="7" t="s">
+      <c r="B91" s="5" t="s">
         <v>201</v>
       </c>
       <c r="C91" s="2" t="s">
@@ -3258,7 +3861,7 @@
       <c r="A92" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="B92" s="7" t="s">
+      <c r="B92" s="5" t="s">
         <v>202</v>
       </c>
       <c r="C92" s="2" t="s">
@@ -3270,7 +3873,7 @@
       <c r="A93" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="B93" s="7" t="s">
+      <c r="B93" s="5" t="s">
         <v>203</v>
       </c>
       <c r="C93" s="2" t="s">
@@ -3282,7 +3885,7 @@
       <c r="A94" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="B94" s="7" t="s">
+      <c r="B94" s="5" t="s">
         <v>204</v>
       </c>
       <c r="C94" s="2" t="s">
@@ -3294,7 +3897,7 @@
       <c r="A95" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="B95" s="7" t="s">
+      <c r="B95" s="5" t="s">
         <v>205</v>
       </c>
       <c r="C95" s="2" t="s">
@@ -3306,7 +3909,7 @@
       <c r="A96" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="B96" s="7" t="s">
+      <c r="B96" s="5" t="s">
         <v>206</v>
       </c>
       <c r="C96" s="2" t="s">
@@ -3318,7 +3921,7 @@
       <c r="A97" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="B97" s="7" t="s">
+      <c r="B97" s="5" t="s">
         <v>207</v>
       </c>
       <c r="C97" s="2" t="s">
@@ -3330,7 +3933,7 @@
       <c r="A98" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="B98" s="7" t="s">
+      <c r="B98" s="5" t="s">
         <v>208</v>
       </c>
       <c r="C98" s="2" t="s">
@@ -3342,7 +3945,7 @@
       <c r="A99" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="B99" s="7" t="s">
+      <c r="B99" s="5" t="s">
         <v>209</v>
       </c>
       <c r="C99" s="2" t="s">
@@ -3354,7 +3957,7 @@
       <c r="A100" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="B100" s="7" t="s">
+      <c r="B100" s="5" t="s">
         <v>210</v>
       </c>
       <c r="C100" s="2" t="s">
@@ -3366,7 +3969,7 @@
       <c r="A101" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="B101" s="7" t="s">
+      <c r="B101" s="5" t="s">
         <v>211</v>
       </c>
       <c r="C101" s="2" t="s">
@@ -3378,7 +3981,7 @@
       <c r="A102" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="B102" s="7" t="s">
+      <c r="B102" s="5" t="s">
         <v>212</v>
       </c>
       <c r="C102" s="2" t="s">
@@ -3393,7 +3996,7 @@
       <c r="A103" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="B103" s="7" t="s">
+      <c r="B103" s="5" t="s">
         <v>213</v>
       </c>
       <c r="C103" s="2" t="s">
@@ -3405,7 +4008,7 @@
       <c r="A104" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="B104" s="7" t="s">
+      <c r="B104" s="5" t="s">
         <v>214</v>
       </c>
       <c r="C104" s="2" t="s">
@@ -3417,7 +4020,7 @@
       <c r="A105" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="B105" s="7" t="s">
+      <c r="B105" s="5" t="s">
         <v>215</v>
       </c>
       <c r="C105" s="2" t="s">
@@ -3429,7 +4032,7 @@
       <c r="A106" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="B106" s="7" t="s">
+      <c r="B106" s="5" t="s">
         <v>232</v>
       </c>
       <c r="C106" s="2" t="s">
@@ -3441,7 +4044,7 @@
       <c r="A107" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="B107" s="7" t="s">
+      <c r="B107" s="5" t="s">
         <v>233</v>
       </c>
       <c r="C107" s="2" t="s">
@@ -3453,7 +4056,7 @@
       <c r="A108" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="B108" s="7" t="s">
+      <c r="B108" s="5" t="s">
         <v>234</v>
       </c>
       <c r="C108" s="2" t="s">
@@ -3465,7 +4068,7 @@
       <c r="A109" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="B109" s="7" t="s">
+      <c r="B109" s="5" t="s">
         <v>235</v>
       </c>
       <c r="C109" s="2" t="s">
@@ -3477,7 +4080,7 @@
       <c r="A110" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="B110" s="7" t="s">
+      <c r="B110" s="5" t="s">
         <v>236</v>
       </c>
       <c r="C110" s="2" t="s">
@@ -3489,7 +4092,7 @@
       <c r="A111" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="B111" s="7" t="s">
+      <c r="B111" s="5" t="s">
         <v>237</v>
       </c>
       <c r="C111" s="2" t="s">
@@ -3501,7 +4104,7 @@
       <c r="A112" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="B112" s="7" t="s">
+      <c r="B112" s="5" t="s">
         <v>238</v>
       </c>
       <c r="C112" s="2" t="s">
@@ -3513,7 +4116,7 @@
       <c r="A113" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="B113" s="7" t="s">
+      <c r="B113" s="5" t="s">
         <v>239</v>
       </c>
       <c r="C113" s="2" t="s">
@@ -3525,7 +4128,7 @@
       <c r="A114" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="B114" s="7" t="s">
+      <c r="B114" s="5" t="s">
         <v>240</v>
       </c>
       <c r="C114" s="2" t="s">
@@ -3537,7 +4140,7 @@
       <c r="A115" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="B115" s="7" t="s">
+      <c r="B115" s="5" t="s">
         <v>241</v>
       </c>
       <c r="C115" s="2" t="s">
@@ -3549,7 +4152,7 @@
       <c r="A116" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="B116" s="7" t="s">
+      <c r="B116" s="5" t="s">
         <v>242</v>
       </c>
       <c r="C116" s="2" t="s">
@@ -3561,7 +4164,7 @@
       <c r="A117" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="B117" s="7" t="s">
+      <c r="B117" s="5" t="s">
         <v>243</v>
       </c>
       <c r="C117" s="2" t="s">
@@ -3573,7 +4176,7 @@
       <c r="A118" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="B118" s="7" t="s">
+      <c r="B118" s="5" t="s">
         <v>244</v>
       </c>
       <c r="C118" s="2" t="s">
@@ -3585,7 +4188,7 @@
       <c r="A119" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="B119" s="7" t="s">
+      <c r="B119" s="5" t="s">
         <v>245</v>
       </c>
       <c r="C119" s="2" t="s">
@@ -3597,7 +4200,7 @@
       <c r="A120" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="B120" s="7" t="s">
+      <c r="B120" s="5" t="s">
         <v>246</v>
       </c>
       <c r="C120" s="2" t="s">
@@ -3609,7 +4212,7 @@
       <c r="A121" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="B121" s="7" t="s">
+      <c r="B121" s="5" t="s">
         <v>283</v>
       </c>
       <c r="C121" s="2" t="s">
@@ -3621,7 +4224,7 @@
       <c r="A122" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="B122" s="7" t="s">
+      <c r="B122" s="5" t="s">
         <v>284</v>
       </c>
       <c r="C122" s="2" t="s">
@@ -3633,7 +4236,7 @@
       <c r="A123" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="B123" s="7" t="s">
+      <c r="B123" s="5" t="s">
         <v>285</v>
       </c>
       <c r="C123" s="2" t="s">
@@ -3645,7 +4248,7 @@
       <c r="A124" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="B124" s="7" t="s">
+      <c r="B124" s="5" t="s">
         <v>286</v>
       </c>
       <c r="C124" s="2" t="s">
@@ -3657,7 +4260,7 @@
       <c r="A125" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="B125" s="7" t="s">
+      <c r="B125" s="5" t="s">
         <v>287</v>
       </c>
       <c r="C125" s="2" t="s">
@@ -3669,7 +4272,7 @@
       <c r="A126" s="5" t="s">
         <v>253</v>
       </c>
-      <c r="B126" s="7" t="s">
+      <c r="B126" s="5" t="s">
         <v>288</v>
       </c>
       <c r="C126" s="2" t="s">
@@ -3681,7 +4284,7 @@
       <c r="A127" s="5" t="s">
         <v>254</v>
       </c>
-      <c r="B127" s="7" t="s">
+      <c r="B127" s="5" t="s">
         <v>289</v>
       </c>
       <c r="C127" s="2" t="s">
@@ -3693,7 +4296,7 @@
       <c r="A128" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="B128" s="7" t="s">
+      <c r="B128" s="5" t="s">
         <v>290</v>
       </c>
       <c r="C128" s="2" t="s">
@@ -3705,7 +4308,7 @@
       <c r="A129" s="5" t="s">
         <v>256</v>
       </c>
-      <c r="B129" s="7" t="s">
+      <c r="B129" s="5" t="s">
         <v>291</v>
       </c>
       <c r="C129" s="2" t="s">
@@ -3717,7 +4320,7 @@
       <c r="A130" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="B130" s="7" t="s">
+      <c r="B130" s="5" t="s">
         <v>292</v>
       </c>
       <c r="C130" s="2" t="s">
@@ -3729,7 +4332,7 @@
       <c r="A131" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="B131" s="7" t="s">
+      <c r="B131" s="5" t="s">
         <v>293</v>
       </c>
       <c r="C131" s="2" t="s">
@@ -3741,7 +4344,7 @@
       <c r="A132" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="B132" s="7" t="s">
+      <c r="B132" s="5" t="s">
         <v>294</v>
       </c>
       <c r="C132" s="2" t="s">
@@ -3753,7 +4356,7 @@
       <c r="A133" s="5" t="s">
         <v>260</v>
       </c>
-      <c r="B133" s="7" t="s">
+      <c r="B133" s="5" t="s">
         <v>295</v>
       </c>
       <c r="C133" s="2" t="s">
@@ -3765,7 +4368,7 @@
       <c r="A134" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="B134" s="7" t="s">
+      <c r="B134" s="5" t="s">
         <v>296</v>
       </c>
       <c r="C134" s="2" t="s">
@@ -3777,7 +4380,7 @@
       <c r="A135" s="5" t="s">
         <v>262</v>
       </c>
-      <c r="B135" s="7" t="s">
+      <c r="B135" s="5" t="s">
         <v>297</v>
       </c>
       <c r="C135" s="2" t="s">
@@ -3789,7 +4392,7 @@
       <c r="A136" s="5" t="s">
         <v>263</v>
       </c>
-      <c r="B136" s="7" t="s">
+      <c r="B136" s="5" t="s">
         <v>298</v>
       </c>
       <c r="C136" s="2" t="s">
@@ -3801,7 +4404,7 @@
       <c r="A137" s="5" t="s">
         <v>264</v>
       </c>
-      <c r="B137" s="7" t="s">
+      <c r="B137" s="5" t="s">
         <v>299</v>
       </c>
       <c r="C137" s="2" t="s">
@@ -3813,7 +4416,7 @@
       <c r="A138" s="5" t="s">
         <v>265</v>
       </c>
-      <c r="B138" s="7" t="s">
+      <c r="B138" s="5" t="s">
         <v>300</v>
       </c>
       <c r="C138" s="2" t="s">
@@ -3825,7 +4428,7 @@
       <c r="A139" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="B139" s="7" t="s">
+      <c r="B139" s="5" t="s">
         <v>301</v>
       </c>
       <c r="C139" s="2" t="s">
@@ -3837,7 +4440,7 @@
       <c r="A140" s="5" t="s">
         <v>267</v>
       </c>
-      <c r="B140" s="7" t="s">
+      <c r="B140" s="5" t="s">
         <v>302</v>
       </c>
       <c r="C140" s="2" t="s">
@@ -3849,7 +4452,7 @@
       <c r="A141" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="B141" s="7" t="s">
+      <c r="B141" s="5" t="s">
         <v>303</v>
       </c>
       <c r="C141" s="2" t="s">
@@ -3861,7 +4464,7 @@
       <c r="A142" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="B142" s="7" t="s">
+      <c r="B142" s="5" t="s">
         <v>304</v>
       </c>
       <c r="C142" s="2" t="s">
@@ -3873,7 +4476,7 @@
       <c r="A143" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="B143" s="7" t="s">
+      <c r="B143" s="5" t="s">
         <v>305</v>
       </c>
       <c r="C143" s="2" t="s">
@@ -3885,7 +4488,7 @@
       <c r="A144" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="B144" s="7" t="s">
+      <c r="B144" s="5" t="s">
         <v>306</v>
       </c>
       <c r="C144" s="2" t="s">
@@ -3897,7 +4500,7 @@
       <c r="A145" s="5" t="s">
         <v>272</v>
       </c>
-      <c r="B145" s="7" t="s">
+      <c r="B145" s="5" t="s">
         <v>307</v>
       </c>
       <c r="C145" s="2" t="s">
@@ -3909,7 +4512,7 @@
       <c r="A146" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="B146" s="7" t="s">
+      <c r="B146" s="5" t="s">
         <v>308</v>
       </c>
       <c r="C146" s="2" t="s">
@@ -3921,7 +4524,7 @@
       <c r="A147" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="B147" s="7" t="s">
+      <c r="B147" s="5" t="s">
         <v>309</v>
       </c>
       <c r="C147" s="2" t="s">
@@ -3933,7 +4536,7 @@
       <c r="A148" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="B148" s="7" t="s">
+      <c r="B148" s="5" t="s">
         <v>310</v>
       </c>
       <c r="C148" s="2" t="s">
@@ -3945,7 +4548,7 @@
       <c r="A149" s="5" t="s">
         <v>276</v>
       </c>
-      <c r="B149" s="7" t="s">
+      <c r="B149" s="5" t="s">
         <v>311</v>
       </c>
       <c r="C149" s="2" t="s">
@@ -3957,7 +4560,7 @@
       <c r="A150" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="B150" s="7" t="s">
+      <c r="B150" s="5" t="s">
         <v>312</v>
       </c>
       <c r="C150" s="2" t="s">
@@ -3972,7 +4575,7 @@
       <c r="A151" s="5" t="s">
         <v>278</v>
       </c>
-      <c r="B151" s="7" t="s">
+      <c r="B151" s="5" t="s">
         <v>313</v>
       </c>
       <c r="C151" s="2" t="s">
@@ -3984,7 +4587,7 @@
       <c r="A152" s="5" t="s">
         <v>279</v>
       </c>
-      <c r="B152" s="7" t="s">
+      <c r="B152" s="5" t="s">
         <v>314</v>
       </c>
       <c r="C152" s="2" t="s">
@@ -3996,7 +4599,7 @@
       <c r="A153" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="B153" s="7" t="s">
+      <c r="B153" s="5" t="s">
         <v>315</v>
       </c>
       <c r="C153" s="2" t="s">
@@ -4008,7 +4611,7 @@
       <c r="A154" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="B154" s="7" t="s">
+      <c r="B154" s="5" t="s">
         <v>316</v>
       </c>
       <c r="C154" s="2" t="s">
@@ -4020,7 +4623,7 @@
       <c r="A155" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="B155" s="7" t="s">
+      <c r="B155" s="5" t="s">
         <v>317</v>
       </c>
       <c r="C155" s="2" t="s">
@@ -4032,7 +4635,7 @@
       <c r="A156" s="5" t="s">
         <v>319</v>
       </c>
-      <c r="B156" s="7" t="s">
+      <c r="B156" s="5" t="s">
         <v>324</v>
       </c>
       <c r="C156" s="2" t="s">
@@ -4044,7 +4647,7 @@
       <c r="A157" s="5" t="s">
         <v>320</v>
       </c>
-      <c r="B157" s="7" t="s">
+      <c r="B157" s="5" t="s">
         <v>325</v>
       </c>
       <c r="C157" s="2" t="s">
@@ -4056,7 +4659,7 @@
       <c r="A158" s="5" t="s">
         <v>321</v>
       </c>
-      <c r="B158" s="7" t="s">
+      <c r="B158" s="5" t="s">
         <v>326</v>
       </c>
       <c r="C158" s="2" t="s">
@@ -4068,7 +4671,7 @@
       <c r="A159" s="5" t="s">
         <v>322</v>
       </c>
-      <c r="B159" s="7" t="s">
+      <c r="B159" s="5" t="s">
         <v>327</v>
       </c>
       <c r="C159" s="2" t="s">
@@ -4080,7 +4683,7 @@
       <c r="A160" s="5" t="s">
         <v>323</v>
       </c>
-      <c r="B160" s="7" t="s">
+      <c r="B160" s="5" t="s">
         <v>328</v>
       </c>
       <c r="C160" s="2" t="s">
@@ -4092,7 +4695,7 @@
       <c r="A161" s="5" t="s">
         <v>330</v>
       </c>
-      <c r="B161" s="7" t="s">
+      <c r="B161" s="5" t="s">
         <v>342</v>
       </c>
       <c r="C161" s="2" t="s">
@@ -4104,7 +4707,7 @@
       <c r="A162" s="5" t="s">
         <v>331</v>
       </c>
-      <c r="B162" s="7" t="s">
+      <c r="B162" s="5" t="s">
         <v>343</v>
       </c>
       <c r="C162" s="2" t="s">
@@ -4116,7 +4719,7 @@
       <c r="A163" s="5" t="s">
         <v>332</v>
       </c>
-      <c r="B163" s="7" t="s">
+      <c r="B163" s="5" t="s">
         <v>344</v>
       </c>
       <c r="C163" s="2" t="s">
@@ -4128,7 +4731,7 @@
       <c r="A164" s="5" t="s">
         <v>333</v>
       </c>
-      <c r="B164" s="7" t="s">
+      <c r="B164" s="5" t="s">
         <v>345</v>
       </c>
       <c r="C164" s="2" t="s">
@@ -4140,7 +4743,7 @@
       <c r="A165" s="5" t="s">
         <v>334</v>
       </c>
-      <c r="B165" s="7" t="s">
+      <c r="B165" s="5" t="s">
         <v>346</v>
       </c>
       <c r="C165" s="2" t="s">
@@ -4152,7 +4755,7 @@
       <c r="A166" s="5" t="s">
         <v>335</v>
       </c>
-      <c r="B166" s="7" t="s">
+      <c r="B166" s="5" t="s">
         <v>347</v>
       </c>
       <c r="C166" s="2" t="s">
@@ -4164,7 +4767,7 @@
       <c r="A167" s="5" t="s">
         <v>336</v>
       </c>
-      <c r="B167" s="7" t="s">
+      <c r="B167" s="5" t="s">
         <v>348</v>
       </c>
       <c r="C167" s="2" t="s">
@@ -4176,7 +4779,7 @@
       <c r="A168" s="5" t="s">
         <v>337</v>
       </c>
-      <c r="B168" s="7" t="s">
+      <c r="B168" s="5" t="s">
         <v>349</v>
       </c>
       <c r="C168" s="2" t="s">
@@ -4188,7 +4791,7 @@
       <c r="A169" s="5" t="s">
         <v>338</v>
       </c>
-      <c r="B169" s="7" t="s">
+      <c r="B169" s="5" t="s">
         <v>350</v>
       </c>
       <c r="C169" s="2" t="s">
@@ -4200,7 +4803,7 @@
       <c r="A170" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="B170" s="7" t="s">
+      <c r="B170" s="5" t="s">
         <v>351</v>
       </c>
       <c r="C170" s="2" t="s">
@@ -4212,7 +4815,7 @@
       <c r="A171" s="5" t="s">
         <v>340</v>
       </c>
-      <c r="B171" s="7" t="s">
+      <c r="B171" s="5" t="s">
         <v>352</v>
       </c>
       <c r="C171" s="2" t="s">
@@ -4224,7 +4827,7 @@
       <c r="A172" s="5" t="s">
         <v>341</v>
       </c>
-      <c r="B172" s="7" t="s">
+      <c r="B172" s="5" t="s">
         <v>353</v>
       </c>
       <c r="C172" s="2" t="s">
@@ -4236,7 +4839,7 @@
       <c r="A173" s="5" t="s">
         <v>354</v>
       </c>
-      <c r="B173" s="7" t="s">
+      <c r="B173" s="5" t="s">
         <v>369</v>
       </c>
       <c r="C173" s="2" t="s">
@@ -4248,7 +4851,7 @@
       <c r="A174" s="5" t="s">
         <v>355</v>
       </c>
-      <c r="B174" s="7" t="s">
+      <c r="B174" s="5" t="s">
         <v>370</v>
       </c>
       <c r="C174" s="2" t="s">
@@ -4260,7 +4863,7 @@
       <c r="A175" s="5" t="s">
         <v>356</v>
       </c>
-      <c r="B175" s="7" t="s">
+      <c r="B175" s="5" t="s">
         <v>371</v>
       </c>
       <c r="C175" s="2" t="s">
@@ -4272,7 +4875,7 @@
       <c r="A176" s="5" t="s">
         <v>357</v>
       </c>
-      <c r="B176" s="7" t="s">
+      <c r="B176" s="5" t="s">
         <v>372</v>
       </c>
       <c r="C176" s="2" t="s">
@@ -4284,7 +4887,7 @@
       <c r="A177" s="5" t="s">
         <v>358</v>
       </c>
-      <c r="B177" s="7" t="s">
+      <c r="B177" s="5" t="s">
         <v>373</v>
       </c>
       <c r="C177" s="2" t="s">
@@ -4296,7 +4899,7 @@
       <c r="A178" s="5" t="s">
         <v>359</v>
       </c>
-      <c r="B178" s="7" t="s">
+      <c r="B178" s="5" t="s">
         <v>374</v>
       </c>
       <c r="C178" s="2" t="s">
@@ -4308,7 +4911,7 @@
       <c r="A179" s="5" t="s">
         <v>360</v>
       </c>
-      <c r="B179" s="7" t="s">
+      <c r="B179" s="5" t="s">
         <v>375</v>
       </c>
       <c r="C179" s="2" t="s">
@@ -4320,7 +4923,7 @@
       <c r="A180" s="5" t="s">
         <v>361</v>
       </c>
-      <c r="B180" s="7" t="s">
+      <c r="B180" s="5" t="s">
         <v>376</v>
       </c>
       <c r="C180" s="2" t="s">
@@ -4332,7 +4935,7 @@
       <c r="A181" s="5" t="s">
         <v>362</v>
       </c>
-      <c r="B181" s="7" t="s">
+      <c r="B181" s="5" t="s">
         <v>377</v>
       </c>
       <c r="C181" s="2" t="s">
@@ -4344,7 +4947,7 @@
       <c r="A182" s="5" t="s">
         <v>363</v>
       </c>
-      <c r="B182" s="7" t="s">
+      <c r="B182" s="5" t="s">
         <v>378</v>
       </c>
       <c r="C182" s="2" t="s">
@@ -4356,7 +4959,7 @@
       <c r="A183" s="5" t="s">
         <v>364</v>
       </c>
-      <c r="B183" s="7" t="s">
+      <c r="B183" s="5" t="s">
         <v>379</v>
       </c>
       <c r="C183" s="2" t="s">
@@ -4368,7 +4971,7 @@
       <c r="A184" s="5" t="s">
         <v>365</v>
       </c>
-      <c r="B184" s="7" t="s">
+      <c r="B184" s="5" t="s">
         <v>380</v>
       </c>
       <c r="C184" s="2" t="s">
@@ -4380,7 +4983,7 @@
       <c r="A185" s="5" t="s">
         <v>366</v>
       </c>
-      <c r="B185" s="7" t="s">
+      <c r="B185" s="5" t="s">
         <v>381</v>
       </c>
       <c r="C185" s="2" t="s">
@@ -4392,7 +4995,7 @@
       <c r="A186" s="5" t="s">
         <v>367</v>
       </c>
-      <c r="B186" s="7" t="s">
+      <c r="B186" s="5" t="s">
         <v>382</v>
       </c>
       <c r="C186" s="2" t="s">
@@ -4404,7 +5007,7 @@
       <c r="A187" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="B187" s="7" t="s">
+      <c r="B187" s="5" t="s">
         <v>383</v>
       </c>
       <c r="C187" s="2" t="s">
@@ -4419,7 +5022,7 @@
       <c r="A188" s="5" t="s">
         <v>385</v>
       </c>
-      <c r="B188" s="7" t="s">
+      <c r="B188" s="5" t="s">
         <v>409</v>
       </c>
       <c r="C188" s="2" t="s">
@@ -4431,7 +5034,7 @@
       <c r="A189" s="5" t="s">
         <v>386</v>
       </c>
-      <c r="B189" s="7" t="s">
+      <c r="B189" s="5" t="s">
         <v>410</v>
       </c>
       <c r="C189" s="2" t="s">
@@ -4443,7 +5046,7 @@
       <c r="A190" s="5" t="s">
         <v>387</v>
       </c>
-      <c r="B190" s="7" t="s">
+      <c r="B190" s="5" t="s">
         <v>411</v>
       </c>
       <c r="C190" s="2" t="s">
@@ -4455,7 +5058,7 @@
       <c r="A191" s="5" t="s">
         <v>388</v>
       </c>
-      <c r="B191" s="7" t="s">
+      <c r="B191" s="5" t="s">
         <v>412</v>
       </c>
       <c r="C191" s="2" t="s">
@@ -4467,7 +5070,7 @@
       <c r="A192" s="5" t="s">
         <v>389</v>
       </c>
-      <c r="B192" s="7" t="s">
+      <c r="B192" s="5" t="s">
         <v>413</v>
       </c>
       <c r="C192" s="2" t="s">
@@ -4479,7 +5082,7 @@
       <c r="A193" s="5" t="s">
         <v>390</v>
       </c>
-      <c r="B193" s="7" t="s">
+      <c r="B193" s="5" t="s">
         <v>414</v>
       </c>
       <c r="C193" s="2" t="s">
@@ -4491,7 +5094,7 @@
       <c r="A194" s="5" t="s">
         <v>391</v>
       </c>
-      <c r="B194" s="7" t="s">
+      <c r="B194" s="5" t="s">
         <v>415</v>
       </c>
       <c r="C194" s="2" t="s">
@@ -4503,7 +5106,7 @@
       <c r="A195" s="5" t="s">
         <v>392</v>
       </c>
-      <c r="B195" s="7" t="s">
+      <c r="B195" s="5" t="s">
         <v>416</v>
       </c>
       <c r="C195" s="2" t="s">
@@ -4515,7 +5118,7 @@
       <c r="A196" s="5" t="s">
         <v>393</v>
       </c>
-      <c r="B196" s="7" t="s">
+      <c r="B196" s="5" t="s">
         <v>417</v>
       </c>
       <c r="C196" s="2" t="s">
@@ -4527,7 +5130,7 @@
       <c r="A197" s="5" t="s">
         <v>394</v>
       </c>
-      <c r="B197" s="7" t="s">
+      <c r="B197" s="5" t="s">
         <v>418</v>
       </c>
       <c r="C197" s="2" t="s">
@@ -4542,7 +5145,7 @@
       <c r="A198" s="5" t="s">
         <v>395</v>
       </c>
-      <c r="B198" s="7" t="s">
+      <c r="B198" s="5" t="s">
         <v>419</v>
       </c>
       <c r="C198" s="2" t="s">
@@ -4554,7 +5157,7 @@
       <c r="A199" s="5" t="s">
         <v>396</v>
       </c>
-      <c r="B199" s="7" t="s">
+      <c r="B199" s="5" t="s">
         <v>420</v>
       </c>
       <c r="C199" s="2" t="s">
@@ -4566,7 +5169,7 @@
       <c r="A200" s="5" t="s">
         <v>397</v>
       </c>
-      <c r="B200" s="7" t="s">
+      <c r="B200" s="5" t="s">
         <v>421</v>
       </c>
       <c r="C200" s="2" t="s">
@@ -4578,7 +5181,7 @@
       <c r="A201" s="5" t="s">
         <v>398</v>
       </c>
-      <c r="B201" s="7" t="s">
+      <c r="B201" s="5" t="s">
         <v>422</v>
       </c>
       <c r="C201" s="2" t="s">
@@ -4590,7 +5193,7 @@
       <c r="A202" s="5" t="s">
         <v>399</v>
       </c>
-      <c r="B202" s="7" t="s">
+      <c r="B202" s="5" t="s">
         <v>423</v>
       </c>
       <c r="C202" s="2" t="s">
@@ -4602,7 +5205,7 @@
       <c r="A203" s="5" t="s">
         <v>400</v>
       </c>
-      <c r="B203" s="7" t="s">
+      <c r="B203" s="5" t="s">
         <v>424</v>
       </c>
       <c r="C203" s="2" t="s">
@@ -4614,7 +5217,7 @@
       <c r="A204" s="5" t="s">
         <v>401</v>
       </c>
-      <c r="B204" s="7" t="s">
+      <c r="B204" s="5" t="s">
         <v>425</v>
       </c>
       <c r="C204" s="2" t="s">
@@ -4626,7 +5229,7 @@
       <c r="A205" s="5" t="s">
         <v>402</v>
       </c>
-      <c r="B205" s="7" t="s">
+      <c r="B205" s="5" t="s">
         <v>426</v>
       </c>
       <c r="C205" s="2" t="s">
@@ -4638,7 +5241,7 @@
       <c r="A206" s="5" t="s">
         <v>403</v>
       </c>
-      <c r="B206" s="7" t="s">
+      <c r="B206" s="5" t="s">
         <v>427</v>
       </c>
       <c r="C206" s="2" t="s">
@@ -4650,7 +5253,7 @@
       <c r="A207" s="5" t="s">
         <v>404</v>
       </c>
-      <c r="B207" s="7" t="s">
+      <c r="B207" s="5" t="s">
         <v>428</v>
       </c>
       <c r="C207" s="2" t="s">
@@ -4662,7 +5265,7 @@
       <c r="A208" s="5" t="s">
         <v>405</v>
       </c>
-      <c r="B208" s="7" t="s">
+      <c r="B208" s="5" t="s">
         <v>429</v>
       </c>
       <c r="C208" s="2" t="s">
@@ -4674,7 +5277,7 @@
       <c r="A209" s="5" t="s">
         <v>406</v>
       </c>
-      <c r="B209" s="7" t="s">
+      <c r="B209" s="5" t="s">
         <v>430</v>
       </c>
       <c r="C209" s="2" t="s">
@@ -4686,7 +5289,7 @@
       <c r="A210" s="5" t="s">
         <v>407</v>
       </c>
-      <c r="B210" s="7" t="s">
+      <c r="B210" s="5" t="s">
         <v>431</v>
       </c>
       <c r="C210" s="2" t="s">
@@ -4698,7 +5301,7 @@
       <c r="A211" s="5" t="s">
         <v>408</v>
       </c>
-      <c r="B211" s="7" t="s">
+      <c r="B211" s="5" t="s">
         <v>432</v>
       </c>
       <c r="C211" s="2" t="s">
@@ -4710,7 +5313,7 @@
       <c r="A212" s="5" t="s">
         <v>434</v>
       </c>
-      <c r="B212" s="7" t="s">
+      <c r="B212" s="5" t="s">
         <v>462</v>
       </c>
       <c r="C212" s="2" t="s">
@@ -4722,7 +5325,7 @@
       <c r="A213" s="5" t="s">
         <v>435</v>
       </c>
-      <c r="B213" s="7" t="s">
+      <c r="B213" s="5" t="s">
         <v>463</v>
       </c>
       <c r="C213" s="2" t="s">
@@ -4734,7 +5337,7 @@
       <c r="A214" s="5" t="s">
         <v>436</v>
       </c>
-      <c r="B214" s="7" t="s">
+      <c r="B214" s="5" t="s">
         <v>464</v>
       </c>
       <c r="C214" s="2" t="s">
@@ -4746,7 +5349,7 @@
       <c r="A215" s="5" t="s">
         <v>437</v>
       </c>
-      <c r="B215" s="7" t="s">
+      <c r="B215" s="5" t="s">
         <v>465</v>
       </c>
       <c r="C215" s="2" t="s">
@@ -4758,7 +5361,7 @@
       <c r="A216" s="5" t="s">
         <v>438</v>
       </c>
-      <c r="B216" s="7" t="s">
+      <c r="B216" s="5" t="s">
         <v>466</v>
       </c>
       <c r="C216" s="2" t="s">
@@ -4770,7 +5373,7 @@
       <c r="A217" s="5" t="s">
         <v>439</v>
       </c>
-      <c r="B217" s="7" t="s">
+      <c r="B217" s="5" t="s">
         <v>467</v>
       </c>
       <c r="C217" s="2" t="s">
@@ -4782,7 +5385,7 @@
       <c r="A218" s="5" t="s">
         <v>440</v>
       </c>
-      <c r="B218" s="7" t="s">
+      <c r="B218" s="5" t="s">
         <v>468</v>
       </c>
       <c r="C218" s="2" t="s">
@@ -4794,7 +5397,7 @@
       <c r="A219" s="5" t="s">
         <v>441</v>
       </c>
-      <c r="B219" s="7" t="s">
+      <c r="B219" s="5" t="s">
         <v>469</v>
       </c>
       <c r="C219" s="2" t="s">
@@ -4806,7 +5409,7 @@
       <c r="A220" s="5" t="s">
         <v>442</v>
       </c>
-      <c r="B220" s="7" t="s">
+      <c r="B220" s="5" t="s">
         <v>470</v>
       </c>
       <c r="C220" s="2" t="s">
@@ -4818,7 +5421,7 @@
       <c r="A221" s="5" t="s">
         <v>443</v>
       </c>
-      <c r="B221" s="7" t="s">
+      <c r="B221" s="5" t="s">
         <v>471</v>
       </c>
       <c r="C221" s="2" t="s">
@@ -4830,7 +5433,7 @@
       <c r="A222" s="5" t="s">
         <v>444</v>
       </c>
-      <c r="B222" s="7" t="s">
+      <c r="B222" s="5" t="s">
         <v>472</v>
       </c>
       <c r="C222" s="2" t="s">
@@ -4842,7 +5445,7 @@
       <c r="A223" s="5" t="s">
         <v>445</v>
       </c>
-      <c r="B223" s="7" t="s">
+      <c r="B223" s="5" t="s">
         <v>473</v>
       </c>
       <c r="C223" s="2" t="s">
@@ -4854,7 +5457,7 @@
       <c r="A224" s="5" t="s">
         <v>446</v>
       </c>
-      <c r="B224" s="7" t="s">
+      <c r="B224" s="5" t="s">
         <v>474</v>
       </c>
       <c r="C224" s="2" t="s">
@@ -4866,7 +5469,7 @@
       <c r="A225" s="5" t="s">
         <v>447</v>
       </c>
-      <c r="B225" s="7" t="s">
+      <c r="B225" s="5" t="s">
         <v>475</v>
       </c>
       <c r="C225" s="2" t="s">
@@ -4878,7 +5481,7 @@
       <c r="A226" s="5" t="s">
         <v>448</v>
       </c>
-      <c r="B226" s="7" t="s">
+      <c r="B226" s="5" t="s">
         <v>476</v>
       </c>
       <c r="C226" s="2" t="s">
@@ -4890,7 +5493,7 @@
       <c r="A227" s="5" t="s">
         <v>449</v>
       </c>
-      <c r="B227" s="7" t="s">
+      <c r="B227" s="5" t="s">
         <v>477</v>
       </c>
       <c r="C227" s="2" t="s">
@@ -4902,7 +5505,7 @@
       <c r="A228" s="5" t="s">
         <v>450</v>
       </c>
-      <c r="B228" s="7" t="s">
+      <c r="B228" s="5" t="s">
         <v>478</v>
       </c>
       <c r="C228" s="2" t="s">
@@ -4914,7 +5517,7 @@
       <c r="A229" s="5" t="s">
         <v>451</v>
       </c>
-      <c r="B229" s="7" t="s">
+      <c r="B229" s="5" t="s">
         <v>479</v>
       </c>
       <c r="C229" s="2" t="s">
@@ -4926,7 +5529,7 @@
       <c r="A230" s="5" t="s">
         <v>452</v>
       </c>
-      <c r="B230" s="7" t="s">
+      <c r="B230" s="5" t="s">
         <v>480</v>
       </c>
       <c r="C230" s="2" t="s">
@@ -4938,7 +5541,7 @@
       <c r="A231" s="5" t="s">
         <v>453</v>
       </c>
-      <c r="B231" s="7" t="s">
+      <c r="B231" s="5" t="s">
         <v>481</v>
       </c>
       <c r="C231" s="2" t="s">
@@ -4950,7 +5553,7 @@
       <c r="A232" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="B232" s="7" t="s">
+      <c r="B232" s="5" t="s">
         <v>482</v>
       </c>
       <c r="C232" s="2" t="s">
@@ -4962,7 +5565,7 @@
       <c r="A233" s="5" t="s">
         <v>455</v>
       </c>
-      <c r="B233" s="7" t="s">
+      <c r="B233" s="5" t="s">
         <v>483</v>
       </c>
       <c r="C233" s="2" t="s">
@@ -4974,7 +5577,7 @@
       <c r="A234" s="5" t="s">
         <v>456</v>
       </c>
-      <c r="B234" s="7" t="s">
+      <c r="B234" s="5" t="s">
         <v>484</v>
       </c>
       <c r="C234" s="2" t="s">
@@ -4986,7 +5589,7 @@
       <c r="A235" s="5" t="s">
         <v>457</v>
       </c>
-      <c r="B235" s="7" t="s">
+      <c r="B235" s="5" t="s">
         <v>485</v>
       </c>
       <c r="C235" s="2" t="s">
@@ -4998,7 +5601,7 @@
       <c r="A236" s="5" t="s">
         <v>458</v>
       </c>
-      <c r="B236" s="7" t="s">
+      <c r="B236" s="5" t="s">
         <v>486</v>
       </c>
       <c r="C236" s="2" t="s">
@@ -5010,7 +5613,7 @@
       <c r="A237" s="5" t="s">
         <v>459</v>
       </c>
-      <c r="B237" s="7" t="s">
+      <c r="B237" s="5" t="s">
         <v>487</v>
       </c>
       <c r="C237" s="2" t="s">
@@ -5022,7 +5625,7 @@
       <c r="A238" s="5" t="s">
         <v>460</v>
       </c>
-      <c r="B238" s="7" t="s">
+      <c r="B238" s="5" t="s">
         <v>488</v>
       </c>
       <c r="C238" s="2" t="s">
@@ -5034,7 +5637,7 @@
       <c r="A239" s="5" t="s">
         <v>461</v>
       </c>
-      <c r="B239" s="7" t="s">
+      <c r="B239" s="5" t="s">
         <v>489</v>
       </c>
       <c r="C239" s="2" t="s">
@@ -5046,7 +5649,7 @@
       <c r="A240" s="5" t="s">
         <v>492</v>
       </c>
-      <c r="B240" s="7" t="s">
+      <c r="B240" s="5" t="s">
         <v>512</v>
       </c>
       <c r="C240" s="2" t="s">
@@ -5059,7 +5662,7 @@
       <c r="A241" s="5" t="s">
         <v>493</v>
       </c>
-      <c r="B241" s="7" t="s">
+      <c r="B241" s="5" t="s">
         <v>513</v>
       </c>
       <c r="C241" s="2" t="s">
@@ -5072,7 +5675,7 @@
       <c r="A242" s="5" t="s">
         <v>494</v>
       </c>
-      <c r="B242" s="7" t="s">
+      <c r="B242" s="5" t="s">
         <v>514</v>
       </c>
       <c r="C242" s="2" t="s">
@@ -5085,7 +5688,7 @@
       <c r="A243" s="5" t="s">
         <v>495</v>
       </c>
-      <c r="B243" s="7" t="s">
+      <c r="B243" s="5" t="s">
         <v>515</v>
       </c>
       <c r="C243" s="2" t="s">
@@ -5098,7 +5701,7 @@
       <c r="A244" s="5" t="s">
         <v>496</v>
       </c>
-      <c r="B244" s="7" t="s">
+      <c r="B244" s="5" t="s">
         <v>516</v>
       </c>
       <c r="C244" s="2" t="s">
@@ -5111,7 +5714,7 @@
       <c r="A245" s="5" t="s">
         <v>497</v>
       </c>
-      <c r="B245" s="7" t="s">
+      <c r="B245" s="5" t="s">
         <v>517</v>
       </c>
       <c r="C245" s="2" t="s">
@@ -5124,7 +5727,7 @@
       <c r="A246" s="5" t="s">
         <v>499</v>
       </c>
-      <c r="B246" s="7" t="s">
+      <c r="B246" s="5" t="s">
         <v>518</v>
       </c>
       <c r="C246" s="2" t="s">
@@ -5137,7 +5740,7 @@
       <c r="A247" s="5" t="s">
         <v>500</v>
       </c>
-      <c r="B247" s="7" t="s">
+      <c r="B247" s="5" t="s">
         <v>519</v>
       </c>
       <c r="C247" s="2" t="s">
@@ -5150,7 +5753,7 @@
       <c r="A248" s="5" t="s">
         <v>501</v>
       </c>
-      <c r="B248" s="7" t="s">
+      <c r="B248" s="5" t="s">
         <v>520</v>
       </c>
       <c r="C248" s="2" t="s">
@@ -5163,7 +5766,7 @@
       <c r="A249" s="5" t="s">
         <v>502</v>
       </c>
-      <c r="B249" s="7" t="s">
+      <c r="B249" s="5" t="s">
         <v>521</v>
       </c>
       <c r="C249" s="2" t="s">
@@ -5176,7 +5779,7 @@
       <c r="A250" s="5" t="s">
         <v>503</v>
       </c>
-      <c r="B250" s="7" t="s">
+      <c r="B250" s="5" t="s">
         <v>522</v>
       </c>
       <c r="C250" s="2" t="s">
@@ -5189,7 +5792,7 @@
       <c r="A251" s="5" t="s">
         <v>504</v>
       </c>
-      <c r="B251" s="7" t="s">
+      <c r="B251" s="5" t="s">
         <v>523</v>
       </c>
       <c r="C251" s="2" t="s">
@@ -5202,7 +5805,7 @@
       <c r="A252" s="5" t="s">
         <v>505</v>
       </c>
-      <c r="B252" s="7" t="s">
+      <c r="B252" s="5" t="s">
         <v>524</v>
       </c>
       <c r="C252" s="2" t="s">
@@ -5215,7 +5818,7 @@
       <c r="A253" s="5" t="s">
         <v>506</v>
       </c>
-      <c r="B253" s="7" t="s">
+      <c r="B253" s="5" t="s">
         <v>525</v>
       </c>
       <c r="C253" s="2" t="s">
@@ -5228,7 +5831,7 @@
       <c r="A254" s="5" t="s">
         <v>507</v>
       </c>
-      <c r="B254" s="7" t="s">
+      <c r="B254" s="5" t="s">
         <v>526</v>
       </c>
       <c r="C254" s="2" t="s">
@@ -5241,7 +5844,7 @@
       <c r="A255" s="5" t="s">
         <v>508</v>
       </c>
-      <c r="B255" s="7" t="s">
+      <c r="B255" s="5" t="s">
         <v>527</v>
       </c>
       <c r="C255" s="2" t="s">
@@ -5254,7 +5857,7 @@
       <c r="A256" s="5" t="s">
         <v>509</v>
       </c>
-      <c r="B256" s="7" t="s">
+      <c r="B256" s="5" t="s">
         <v>528</v>
       </c>
       <c r="C256" s="2" t="s">
@@ -5267,7 +5870,7 @@
       <c r="A257" s="5" t="s">
         <v>510</v>
       </c>
-      <c r="B257" s="7" t="s">
+      <c r="B257" s="5" t="s">
         <v>529</v>
       </c>
       <c r="C257" s="2" t="s">
@@ -5278,7 +5881,7 @@
       <c r="A258" s="5" t="s">
         <v>511</v>
       </c>
-      <c r="B258" s="7" t="s">
+      <c r="B258" s="5" t="s">
         <v>530</v>
       </c>
       <c r="C258" s="2" t="s">
@@ -5289,7 +5892,7 @@
       <c r="A259" s="5" t="s">
         <v>498</v>
       </c>
-      <c r="B259" s="7" t="s">
+      <c r="B259" s="5" t="s">
         <v>534</v>
       </c>
       <c r="C259" s="2" t="s">
@@ -5300,7 +5903,7 @@
       <c r="A260" s="5" t="s">
         <v>497</v>
       </c>
-      <c r="B260" s="7" t="s">
+      <c r="B260" s="5" t="s">
         <v>535</v>
       </c>
       <c r="C260" s="2" t="s">
@@ -5311,7 +5914,7 @@
       <c r="A261" s="5" t="s">
         <v>532</v>
       </c>
-      <c r="B261" s="7" t="s">
+      <c r="B261" s="5" t="s">
         <v>536</v>
       </c>
       <c r="C261" s="2" t="s">
@@ -5322,7 +5925,7 @@
       <c r="A262" s="5" t="s">
         <v>506</v>
       </c>
-      <c r="B262" s="7" t="s">
+      <c r="B262" s="5" t="s">
         <v>537</v>
       </c>
       <c r="C262" s="2" t="s">
@@ -5333,7 +5936,7 @@
       <c r="A263" s="5" t="s">
         <v>533</v>
       </c>
-      <c r="B263" s="7" t="s">
+      <c r="B263" s="5" t="s">
         <v>538</v>
       </c>
       <c r="C263" s="2" t="s">
@@ -5341,130 +5944,1300 @@
       </c>
     </row>
     <row r="264" spans="1:5" ht="18" customHeight="1">
-      <c r="A264"/>
-      <c r="B264"/>
-      <c r="C264"/>
+      <c r="A264" s="5" t="s">
+        <v>539</v>
+      </c>
+      <c r="B264" s="5" t="s">
+        <v>563</v>
+      </c>
+      <c r="C264" s="2" t="s">
+        <v>587</v>
+      </c>
       <c r="D264"/>
       <c r="E264"/>
     </row>
     <row r="265" spans="1:5" ht="18" customHeight="1">
-      <c r="A265"/>
-      <c r="B265"/>
-      <c r="C265"/>
+      <c r="A265" s="5" t="s">
+        <v>540</v>
+      </c>
+      <c r="B265" s="5" t="s">
+        <v>564</v>
+      </c>
+      <c r="C265" s="2" t="s">
+        <v>587</v>
+      </c>
       <c r="D265"/>
       <c r="E265"/>
     </row>
     <row r="266" spans="1:5" ht="18" customHeight="1">
-      <c r="A266"/>
-      <c r="B266"/>
-      <c r="C266"/>
+      <c r="A266" s="5" t="s">
+        <v>541</v>
+      </c>
+      <c r="B266" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="C266" s="2" t="s">
+        <v>587</v>
+      </c>
       <c r="D266"/>
       <c r="E266"/>
     </row>
     <row r="267" spans="1:5" ht="18" customHeight="1">
-      <c r="A267"/>
-      <c r="B267"/>
-      <c r="C267"/>
+      <c r="A267" s="5" t="s">
+        <v>542</v>
+      </c>
+      <c r="B267" s="5" t="s">
+        <v>566</v>
+      </c>
+      <c r="C267" s="2" t="s">
+        <v>587</v>
+      </c>
       <c r="D267"/>
       <c r="E267"/>
     </row>
     <row r="268" spans="1:5" ht="18" customHeight="1">
-      <c r="A268"/>
-      <c r="B268"/>
-      <c r="C268"/>
+      <c r="A268" s="5" t="s">
+        <v>543</v>
+      </c>
+      <c r="B268" s="5" t="s">
+        <v>567</v>
+      </c>
+      <c r="C268" s="2" t="s">
+        <v>587</v>
+      </c>
       <c r="D268"/>
       <c r="E268"/>
     </row>
     <row r="269" spans="1:5" ht="18" customHeight="1">
-      <c r="A269"/>
-      <c r="B269"/>
-      <c r="C269"/>
+      <c r="A269" s="5" t="s">
+        <v>544</v>
+      </c>
+      <c r="B269" s="5" t="s">
+        <v>568</v>
+      </c>
+      <c r="C269" s="2" t="s">
+        <v>587</v>
+      </c>
       <c r="D269"/>
       <c r="E269"/>
     </row>
     <row r="270" spans="1:5" ht="18" customHeight="1">
-      <c r="A270"/>
-      <c r="B270"/>
-      <c r="C270"/>
+      <c r="A270" s="5" t="s">
+        <v>545</v>
+      </c>
+      <c r="B270" s="5" t="s">
+        <v>569</v>
+      </c>
+      <c r="C270" s="2" t="s">
+        <v>587</v>
+      </c>
       <c r="D270"/>
       <c r="E270"/>
     </row>
     <row r="271" spans="1:5" ht="18" customHeight="1">
-      <c r="A271"/>
-      <c r="B271"/>
-      <c r="C271"/>
+      <c r="A271" s="5" t="s">
+        <v>546</v>
+      </c>
+      <c r="B271" s="5" t="s">
+        <v>570</v>
+      </c>
+      <c r="C271" s="2" t="s">
+        <v>587</v>
+      </c>
       <c r="D271"/>
       <c r="E271"/>
     </row>
     <row r="272" spans="1:5" ht="18" customHeight="1">
-      <c r="A272"/>
-      <c r="B272"/>
-      <c r="C272"/>
+      <c r="A272" s="5" t="s">
+        <v>547</v>
+      </c>
+      <c r="B272" s="5" t="s">
+        <v>571</v>
+      </c>
+      <c r="C272" s="2" t="s">
+        <v>587</v>
+      </c>
       <c r="D272"/>
       <c r="E272"/>
     </row>
     <row r="273" spans="1:5" ht="18" customHeight="1">
-      <c r="A273"/>
-      <c r="B273"/>
-      <c r="C273"/>
+      <c r="A273" s="5" t="s">
+        <v>548</v>
+      </c>
+      <c r="B273" s="5" t="s">
+        <v>572</v>
+      </c>
+      <c r="C273" s="2" t="s">
+        <v>587</v>
+      </c>
       <c r="D273"/>
       <c r="E273"/>
     </row>
     <row r="274" spans="1:5" ht="18" customHeight="1">
-      <c r="A274"/>
-      <c r="B274"/>
-      <c r="C274"/>
+      <c r="A274" s="5" t="s">
+        <v>549</v>
+      </c>
+      <c r="B274" s="5" t="s">
+        <v>573</v>
+      </c>
+      <c r="C274" s="2" t="s">
+        <v>587</v>
+      </c>
       <c r="D274"/>
       <c r="E274"/>
     </row>
     <row r="275" spans="1:5" ht="18" customHeight="1">
-      <c r="A275"/>
-      <c r="B275"/>
-      <c r="C275"/>
+      <c r="A275" s="5" t="s">
+        <v>550</v>
+      </c>
+      <c r="B275" s="5" t="s">
+        <v>574</v>
+      </c>
+      <c r="C275" s="2" t="s">
+        <v>587</v>
+      </c>
       <c r="D275"/>
       <c r="E275"/>
     </row>
     <row r="276" spans="1:5" ht="18" customHeight="1">
-      <c r="A276"/>
-      <c r="B276"/>
-      <c r="C276"/>
+      <c r="A276" s="5" t="s">
+        <v>551</v>
+      </c>
+      <c r="B276" s="5" t="s">
+        <v>575</v>
+      </c>
+      <c r="C276" s="2" t="s">
+        <v>587</v>
+      </c>
       <c r="D276"/>
       <c r="E276"/>
     </row>
     <row r="277" spans="1:5" ht="18" customHeight="1">
-      <c r="A277"/>
-      <c r="B277"/>
-      <c r="C277"/>
+      <c r="A277" s="5" t="s">
+        <v>552</v>
+      </c>
+      <c r="B277" s="5" t="s">
+        <v>576</v>
+      </c>
+      <c r="C277" s="2" t="s">
+        <v>587</v>
+      </c>
       <c r="D277"/>
       <c r="E277"/>
     </row>
     <row r="278" spans="1:5" ht="18" customHeight="1">
-      <c r="A278"/>
-      <c r="B278"/>
-      <c r="C278"/>
+      <c r="A278" s="5" t="s">
+        <v>553</v>
+      </c>
+      <c r="B278" s="5" t="s">
+        <v>577</v>
+      </c>
+      <c r="C278" s="2" t="s">
+        <v>587</v>
+      </c>
       <c r="D278"/>
       <c r="E278"/>
     </row>
     <row r="279" spans="1:5" ht="18" customHeight="1">
-      <c r="A279"/>
-      <c r="B279"/>
-      <c r="C279"/>
+      <c r="A279" s="5" t="s">
+        <v>554</v>
+      </c>
+      <c r="B279" s="5" t="s">
+        <v>578</v>
+      </c>
+      <c r="C279" s="2" t="s">
+        <v>587</v>
+      </c>
       <c r="D279"/>
       <c r="E279"/>
     </row>
     <row r="280" spans="1:5" ht="18" customHeight="1">
-      <c r="A280"/>
-      <c r="B280"/>
-      <c r="C280"/>
+      <c r="A280" s="5" t="s">
+        <v>555</v>
+      </c>
+      <c r="B280" s="5" t="s">
+        <v>579</v>
+      </c>
+      <c r="C280" s="2" t="s">
+        <v>587</v>
+      </c>
       <c r="D280"/>
       <c r="E280"/>
     </row>
     <row r="281" spans="1:5" ht="18" customHeight="1">
-      <c r="A281"/>
-      <c r="B281"/>
-      <c r="C281"/>
-      <c r="D281"/>
-      <c r="E281"/>
+      <c r="A281" s="5" t="s">
+        <v>556</v>
+      </c>
+      <c r="B281" s="5" t="s">
+        <v>580</v>
+      </c>
+      <c r="C281" s="2" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="282" spans="1:5" ht="18" customHeight="1">
+      <c r="A282" s="5" t="s">
+        <v>557</v>
+      </c>
+      <c r="B282" s="5" t="s">
+        <v>581</v>
+      </c>
+      <c r="C282" s="2" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="283" spans="1:5" ht="18" customHeight="1">
+      <c r="A283" s="5" t="s">
+        <v>558</v>
+      </c>
+      <c r="B283" s="5" t="s">
+        <v>582</v>
+      </c>
+      <c r="C283" s="2" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="284" spans="1:5" ht="18" customHeight="1">
+      <c r="A284" s="5" t="s">
+        <v>559</v>
+      </c>
+      <c r="B284" s="5" t="s">
+        <v>583</v>
+      </c>
+      <c r="C284" s="2" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="285" spans="1:5" ht="18" customHeight="1">
+      <c r="A285" s="5" t="s">
+        <v>560</v>
+      </c>
+      <c r="B285" s="5" t="s">
+        <v>584</v>
+      </c>
+      <c r="C285" s="2" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="286" spans="1:5" ht="18" customHeight="1">
+      <c r="A286" s="5" t="s">
+        <v>561</v>
+      </c>
+      <c r="B286" s="5" t="s">
+        <v>585</v>
+      </c>
+      <c r="C286" s="2" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="287" spans="1:5" ht="18" customHeight="1">
+      <c r="A287" s="5" t="s">
+        <v>562</v>
+      </c>
+      <c r="B287" s="5" t="s">
+        <v>586</v>
+      </c>
+      <c r="C287" s="2" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="288" spans="1:5" ht="18" customHeight="1">
+      <c r="A288" s="5" t="s">
+        <v>588</v>
+      </c>
+      <c r="B288" s="5" t="s">
+        <v>592</v>
+      </c>
+      <c r="C288" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="D288"/>
+      <c r="E288"/>
+    </row>
+    <row r="289" spans="1:5" ht="18" customHeight="1">
+      <c r="A289" s="5" t="s">
+        <v>589</v>
+      </c>
+      <c r="B289" s="5" t="s">
+        <v>593</v>
+      </c>
+      <c r="C289" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="D289"/>
+      <c r="E289"/>
+    </row>
+    <row r="290" spans="1:5" ht="18" customHeight="1">
+      <c r="A290" s="5" t="s">
+        <v>590</v>
+      </c>
+      <c r="B290" s="5" t="s">
+        <v>594</v>
+      </c>
+      <c r="C290" s="2" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="291" spans="1:5" ht="18" customHeight="1">
+      <c r="A291" s="5" t="s">
+        <v>591</v>
+      </c>
+      <c r="B291" s="5" t="s">
+        <v>595</v>
+      </c>
+      <c r="C291" s="2" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="292" spans="1:5" ht="18" customHeight="1">
+      <c r="A292" s="5" t="s">
+        <v>559</v>
+      </c>
+      <c r="B292" s="5" t="s">
+        <v>596</v>
+      </c>
+      <c r="C292" s="2" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="293" spans="1:5" ht="18" customHeight="1">
+      <c r="A293" s="5" t="s">
+        <v>597</v>
+      </c>
+      <c r="B293" s="5" t="s">
+        <v>619</v>
+      </c>
+      <c r="C293" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="D293"/>
+      <c r="E293"/>
+    </row>
+    <row r="294" spans="1:5" ht="18" customHeight="1">
+      <c r="A294" s="5" t="s">
+        <v>598</v>
+      </c>
+      <c r="B294" s="5" t="s">
+        <v>620</v>
+      </c>
+      <c r="C294" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="D294"/>
+      <c r="E294"/>
+    </row>
+    <row r="295" spans="1:5" ht="18" customHeight="1">
+      <c r="A295" s="5" t="s">
+        <v>599</v>
+      </c>
+      <c r="B295" s="5" t="s">
+        <v>621</v>
+      </c>
+      <c r="C295" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="D295"/>
+      <c r="E295"/>
+    </row>
+    <row r="296" spans="1:5" ht="18" customHeight="1">
+      <c r="A296" s="5" t="s">
+        <v>600</v>
+      </c>
+      <c r="B296" s="5" t="s">
+        <v>622</v>
+      </c>
+      <c r="C296" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="D296"/>
+      <c r="E296"/>
+    </row>
+    <row r="297" spans="1:5" ht="18" customHeight="1">
+      <c r="A297" s="5" t="s">
+        <v>601</v>
+      </c>
+      <c r="B297" s="5" t="s">
+        <v>623</v>
+      </c>
+      <c r="C297" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="D297"/>
+      <c r="E297"/>
+    </row>
+    <row r="298" spans="1:5" ht="18" customHeight="1">
+      <c r="A298" s="5" t="s">
+        <v>602</v>
+      </c>
+      <c r="B298" s="5" t="s">
+        <v>624</v>
+      </c>
+      <c r="C298" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="D298"/>
+      <c r="E298"/>
+    </row>
+    <row r="299" spans="1:5" ht="18" customHeight="1">
+      <c r="A299" s="5" t="s">
+        <v>603</v>
+      </c>
+      <c r="B299" s="5" t="s">
+        <v>625</v>
+      </c>
+      <c r="C299" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="D299"/>
+      <c r="E299"/>
+    </row>
+    <row r="300" spans="1:5" ht="18" customHeight="1">
+      <c r="A300" s="5" t="s">
+        <v>604</v>
+      </c>
+      <c r="B300" s="5" t="s">
+        <v>626</v>
+      </c>
+      <c r="C300" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="D300"/>
+      <c r="E300"/>
+    </row>
+    <row r="301" spans="1:5" ht="18" customHeight="1">
+      <c r="A301" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="B301" s="5" t="s">
+        <v>627</v>
+      </c>
+      <c r="C301" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="D301"/>
+      <c r="E301"/>
+    </row>
+    <row r="302" spans="1:5" ht="18" customHeight="1">
+      <c r="A302" s="5" t="s">
+        <v>606</v>
+      </c>
+      <c r="B302" s="5" t="s">
+        <v>628</v>
+      </c>
+      <c r="C302" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="D302"/>
+      <c r="E302"/>
+    </row>
+    <row r="303" spans="1:5" ht="18" customHeight="1">
+      <c r="A303" s="5" t="s">
+        <v>607</v>
+      </c>
+      <c r="B303" s="5" t="s">
+        <v>629</v>
+      </c>
+      <c r="C303" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="D303"/>
+      <c r="E303"/>
+    </row>
+    <row r="304" spans="1:5" ht="18" customHeight="1">
+      <c r="A304" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="B304" s="5" t="s">
+        <v>630</v>
+      </c>
+      <c r="C304" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="D304"/>
+      <c r="E304"/>
+    </row>
+    <row r="305" spans="1:5" ht="18" customHeight="1">
+      <c r="A305" s="5" t="s">
+        <v>609</v>
+      </c>
+      <c r="B305" s="5" t="s">
+        <v>631</v>
+      </c>
+      <c r="C305" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="D305"/>
+      <c r="E305"/>
+    </row>
+    <row r="306" spans="1:5" ht="18" customHeight="1">
+      <c r="A306" s="5" t="s">
+        <v>610</v>
+      </c>
+      <c r="B306" s="5" t="s">
+        <v>632</v>
+      </c>
+      <c r="C306" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="D306"/>
+      <c r="E306"/>
+    </row>
+    <row r="307" spans="1:5" ht="18" customHeight="1">
+      <c r="A307" s="5" t="s">
+        <v>611</v>
+      </c>
+      <c r="B307" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="C307" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="D307"/>
+      <c r="E307"/>
+    </row>
+    <row r="308" spans="1:5" ht="18" customHeight="1">
+      <c r="A308" s="5" t="s">
+        <v>612</v>
+      </c>
+      <c r="B308" s="5" t="s">
+        <v>634</v>
+      </c>
+      <c r="C308" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="D308"/>
+      <c r="E308"/>
+    </row>
+    <row r="309" spans="1:5" ht="18" customHeight="1">
+      <c r="A309" s="5" t="s">
+        <v>613</v>
+      </c>
+      <c r="B309" s="5" t="s">
+        <v>635</v>
+      </c>
+      <c r="C309" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="D309"/>
+      <c r="E309"/>
+    </row>
+    <row r="310" spans="1:5" ht="18" customHeight="1">
+      <c r="A310" s="5" t="s">
+        <v>614</v>
+      </c>
+      <c r="B310" s="5" t="s">
+        <v>636</v>
+      </c>
+      <c r="C310" s="2" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="311" spans="1:5" ht="18" customHeight="1">
+      <c r="A311" s="5" t="s">
+        <v>615</v>
+      </c>
+      <c r="B311" s="5" t="s">
+        <v>637</v>
+      </c>
+      <c r="C311" s="2" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="312" spans="1:5" ht="18" customHeight="1">
+      <c r="A312" s="5" t="s">
+        <v>616</v>
+      </c>
+      <c r="B312" s="5" t="s">
+        <v>638</v>
+      </c>
+      <c r="C312" s="2" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="313" spans="1:5" ht="18" customHeight="1">
+      <c r="A313" s="5" t="s">
+        <v>617</v>
+      </c>
+      <c r="B313" s="5" t="s">
+        <v>639</v>
+      </c>
+      <c r="C313" s="2" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="314" spans="1:5" ht="18" customHeight="1">
+      <c r="A314" s="5" t="s">
+        <v>618</v>
+      </c>
+      <c r="B314" s="5" t="s">
+        <v>640</v>
+      </c>
+      <c r="C314" s="2" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="315" spans="1:5" ht="18" customHeight="1">
+      <c r="A315" s="5" t="s">
+        <v>642</v>
+      </c>
+      <c r="B315" s="5" t="s">
+        <v>648</v>
+      </c>
+      <c r="C315" s="2" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="316" spans="1:5" ht="18" customHeight="1">
+      <c r="A316" s="5" t="s">
+        <v>604</v>
+      </c>
+      <c r="B316" s="5" t="s">
+        <v>649</v>
+      </c>
+      <c r="C316" s="2" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="317" spans="1:5" ht="18" customHeight="1">
+      <c r="A317" s="5" t="s">
+        <v>643</v>
+      </c>
+      <c r="B317" s="5" t="s">
+        <v>650</v>
+      </c>
+      <c r="C317" s="2" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="318" spans="1:5" ht="18" customHeight="1">
+      <c r="A318" s="5" t="s">
+        <v>644</v>
+      </c>
+      <c r="B318" s="5" t="s">
+        <v>651</v>
+      </c>
+      <c r="C318" s="2" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="319" spans="1:5" ht="18" customHeight="1">
+      <c r="A319" s="5" t="s">
+        <v>645</v>
+      </c>
+      <c r="B319" s="5" t="s">
+        <v>652</v>
+      </c>
+      <c r="C319" s="2" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="320" spans="1:5" ht="18" customHeight="1">
+      <c r="A320" s="5" t="s">
+        <v>646</v>
+      </c>
+      <c r="B320" s="5" t="s">
+        <v>653</v>
+      </c>
+      <c r="C320" s="2" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="321" spans="1:5" ht="18" customHeight="1">
+      <c r="A321" s="5" t="s">
+        <v>618</v>
+      </c>
+      <c r="B321" s="5" t="s">
+        <v>654</v>
+      </c>
+      <c r="C321" s="2" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="322" spans="1:5" ht="18" customHeight="1">
+      <c r="A322" s="5" t="s">
+        <v>647</v>
+      </c>
+      <c r="B322" s="5" t="s">
+        <v>655</v>
+      </c>
+      <c r="C322" s="2" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="323" spans="1:5" ht="18" customHeight="1">
+      <c r="A323" s="5" t="s">
+        <v>656</v>
+      </c>
+      <c r="B323" s="5" t="s">
+        <v>666</v>
+      </c>
+      <c r="C323" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="D323"/>
+      <c r="E323"/>
+    </row>
+    <row r="324" spans="1:5" ht="18" customHeight="1">
+      <c r="A324" s="5" t="s">
+        <v>657</v>
+      </c>
+      <c r="B324" s="5" t="s">
+        <v>667</v>
+      </c>
+      <c r="C324" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="D324"/>
+      <c r="E324"/>
+    </row>
+    <row r="325" spans="1:5" ht="18" customHeight="1">
+      <c r="A325" s="5" t="s">
+        <v>658</v>
+      </c>
+      <c r="B325" s="5" t="s">
+        <v>668</v>
+      </c>
+      <c r="C325" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="D325"/>
+      <c r="E325"/>
+    </row>
+    <row r="326" spans="1:5" ht="18" customHeight="1">
+      <c r="A326" s="5" t="s">
+        <v>659</v>
+      </c>
+      <c r="B326" s="5" t="s">
+        <v>669</v>
+      </c>
+      <c r="C326" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="D326"/>
+      <c r="E326"/>
+    </row>
+    <row r="327" spans="1:5" ht="18" customHeight="1">
+      <c r="A327" s="5" t="s">
+        <v>660</v>
+      </c>
+      <c r="B327" s="5" t="s">
+        <v>670</v>
+      </c>
+      <c r="C327" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="D327"/>
+      <c r="E327"/>
+    </row>
+    <row r="328" spans="1:5" ht="18" customHeight="1">
+      <c r="A328" s="5" t="s">
+        <v>661</v>
+      </c>
+      <c r="B328" s="5" t="s">
+        <v>671</v>
+      </c>
+      <c r="C328" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="D328"/>
+      <c r="E328"/>
+    </row>
+    <row r="329" spans="1:5" ht="18" customHeight="1">
+      <c r="A329" s="5" t="s">
+        <v>663</v>
+      </c>
+      <c r="B329" s="5" t="s">
+        <v>672</v>
+      </c>
+      <c r="C329" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="D329"/>
+      <c r="E329"/>
+    </row>
+    <row r="330" spans="1:5" ht="18" customHeight="1">
+      <c r="A330" s="5" t="s">
+        <v>664</v>
+      </c>
+      <c r="B330" s="5" t="s">
+        <v>673</v>
+      </c>
+      <c r="C330" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="D330"/>
+      <c r="E330"/>
+    </row>
+    <row r="331" spans="1:5" ht="18" customHeight="1">
+      <c r="A331" s="5" t="s">
+        <v>665</v>
+      </c>
+      <c r="B331" s="5" t="s">
+        <v>674</v>
+      </c>
+      <c r="C331" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="D331"/>
+      <c r="E331"/>
+    </row>
+    <row r="332" spans="1:5" ht="18" customHeight="1">
+      <c r="A332" s="5" t="s">
+        <v>676</v>
+      </c>
+      <c r="B332" s="5" t="s">
+        <v>693</v>
+      </c>
+      <c r="C332" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="D332"/>
+      <c r="E332"/>
+    </row>
+    <row r="333" spans="1:5" ht="18" customHeight="1">
+      <c r="A333" s="5" t="s">
+        <v>659</v>
+      </c>
+      <c r="B333" s="5" t="s">
+        <v>694</v>
+      </c>
+      <c r="C333" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="D333"/>
+      <c r="E333"/>
+    </row>
+    <row r="334" spans="1:5" ht="18" customHeight="1">
+      <c r="A334" s="5" t="s">
+        <v>677</v>
+      </c>
+      <c r="B334" s="5" t="s">
+        <v>695</v>
+      </c>
+      <c r="C334" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="D334"/>
+      <c r="E334"/>
+    </row>
+    <row r="335" spans="1:5" ht="18" customHeight="1">
+      <c r="A335" s="5" t="s">
+        <v>678</v>
+      </c>
+      <c r="B335" s="5" t="s">
+        <v>696</v>
+      </c>
+      <c r="C335" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="D335"/>
+      <c r="E335"/>
+    </row>
+    <row r="336" spans="1:5" ht="18" customHeight="1">
+      <c r="A336" s="5" t="s">
+        <v>679</v>
+      </c>
+      <c r="B336" s="5" t="s">
+        <v>697</v>
+      </c>
+      <c r="C336" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="D336"/>
+      <c r="E336"/>
+    </row>
+    <row r="337" spans="1:5" ht="18" customHeight="1">
+      <c r="A337" s="5" t="s">
+        <v>680</v>
+      </c>
+      <c r="B337" s="5" t="s">
+        <v>698</v>
+      </c>
+      <c r="C337" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="D337"/>
+      <c r="E337"/>
+    </row>
+    <row r="338" spans="1:5" ht="18" customHeight="1">
+      <c r="A338" s="5" t="s">
+        <v>681</v>
+      </c>
+      <c r="B338" s="5" t="s">
+        <v>699</v>
+      </c>
+      <c r="C338" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="D338"/>
+      <c r="E338"/>
+    </row>
+    <row r="339" spans="1:5" ht="18" customHeight="1">
+      <c r="A339" s="5" t="s">
+        <v>682</v>
+      </c>
+      <c r="B339" s="5" t="s">
+        <v>700</v>
+      </c>
+      <c r="C339" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="D339"/>
+      <c r="E339"/>
+    </row>
+    <row r="340" spans="1:5" ht="18" customHeight="1">
+      <c r="A340" s="5" t="s">
+        <v>683</v>
+      </c>
+      <c r="B340" s="5" t="s">
+        <v>701</v>
+      </c>
+      <c r="C340" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="D340"/>
+      <c r="E340"/>
+    </row>
+    <row r="341" spans="1:5" ht="18" customHeight="1">
+      <c r="A341" s="5" t="s">
+        <v>662</v>
+      </c>
+      <c r="B341" s="5" t="s">
+        <v>702</v>
+      </c>
+      <c r="C341" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="D341"/>
+      <c r="E341"/>
+    </row>
+    <row r="342" spans="1:5" ht="18" customHeight="1">
+      <c r="A342" s="5" t="s">
+        <v>684</v>
+      </c>
+      <c r="B342" s="5" t="s">
+        <v>703</v>
+      </c>
+      <c r="C342" s="2" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="343" spans="1:5" ht="18" customHeight="1">
+      <c r="A343" s="5" t="s">
+        <v>685</v>
+      </c>
+      <c r="B343" s="5" t="s">
+        <v>704</v>
+      </c>
+      <c r="C343" s="2" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="344" spans="1:5" ht="18" customHeight="1">
+      <c r="A344" s="5" t="s">
+        <v>686</v>
+      </c>
+      <c r="B344" s="5" t="s">
+        <v>705</v>
+      </c>
+      <c r="C344" s="2" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="345" spans="1:5" ht="18" customHeight="1">
+      <c r="A345" s="5" t="s">
+        <v>687</v>
+      </c>
+      <c r="B345" s="5" t="s">
+        <v>706</v>
+      </c>
+      <c r="C345" s="2" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="346" spans="1:5" ht="18" customHeight="1">
+      <c r="A346" s="5" t="s">
+        <v>688</v>
+      </c>
+      <c r="B346" s="5" t="s">
+        <v>707</v>
+      </c>
+      <c r="C346" s="2" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="347" spans="1:5" ht="18" customHeight="1">
+      <c r="A347" s="5" t="s">
+        <v>689</v>
+      </c>
+      <c r="B347" s="5" t="s">
+        <v>708</v>
+      </c>
+      <c r="C347" s="2" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="348" spans="1:5" ht="18" customHeight="1">
+      <c r="A348" s="5" t="s">
+        <v>690</v>
+      </c>
+      <c r="B348" s="5" t="s">
+        <v>709</v>
+      </c>
+      <c r="C348" s="2" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="349" spans="1:5" ht="18" customHeight="1">
+      <c r="A349" s="5" t="s">
+        <v>691</v>
+      </c>
+      <c r="B349" s="5" t="s">
+        <v>710</v>
+      </c>
+      <c r="C349" s="2" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="350" spans="1:5" ht="18" customHeight="1">
+      <c r="A350" s="5" t="s">
+        <v>692</v>
+      </c>
+      <c r="B350" s="5" t="s">
+        <v>711</v>
+      </c>
+      <c r="C350" s="2" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="351" spans="1:5" ht="18" customHeight="1">
+      <c r="A351" s="5" t="s">
+        <v>712</v>
+      </c>
+      <c r="B351" s="5" t="s">
+        <v>726</v>
+      </c>
+      <c r="C351" s="2" t="s">
+        <v>740</v>
+      </c>
+      <c r="D351"/>
+      <c r="E351"/>
+    </row>
+    <row r="352" spans="1:5" ht="18" customHeight="1">
+      <c r="A352" s="5" t="s">
+        <v>713</v>
+      </c>
+      <c r="B352" s="5" t="s">
+        <v>727</v>
+      </c>
+      <c r="C352" s="2" t="s">
+        <v>740</v>
+      </c>
+      <c r="D352"/>
+      <c r="E352"/>
+    </row>
+    <row r="353" spans="1:5" ht="18" customHeight="1">
+      <c r="A353" s="5" t="s">
+        <v>714</v>
+      </c>
+      <c r="B353" s="5" t="s">
+        <v>728</v>
+      </c>
+      <c r="C353" s="2" t="s">
+        <v>740</v>
+      </c>
+      <c r="D353"/>
+      <c r="E353"/>
+    </row>
+    <row r="354" spans="1:5" ht="18" customHeight="1">
+      <c r="A354" s="5" t="s">
+        <v>715</v>
+      </c>
+      <c r="B354" s="5" t="s">
+        <v>729</v>
+      </c>
+      <c r="C354" s="2" t="s">
+        <v>740</v>
+      </c>
+      <c r="D354"/>
+      <c r="E354"/>
+    </row>
+    <row r="355" spans="1:5" ht="18" customHeight="1">
+      <c r="A355" s="5" t="s">
+        <v>716</v>
+      </c>
+      <c r="B355" s="5" t="s">
+        <v>730</v>
+      </c>
+      <c r="C355" s="2" t="s">
+        <v>740</v>
+      </c>
+      <c r="D355"/>
+      <c r="E355"/>
+    </row>
+    <row r="356" spans="1:5" ht="18" customHeight="1">
+      <c r="A356" s="5" t="s">
+        <v>717</v>
+      </c>
+      <c r="B356" s="5" t="s">
+        <v>731</v>
+      </c>
+      <c r="C356" s="2" t="s">
+        <v>740</v>
+      </c>
+      <c r="D356"/>
+      <c r="E356"/>
+    </row>
+    <row r="357" spans="1:5" ht="18" customHeight="1">
+      <c r="A357" s="5" t="s">
+        <v>718</v>
+      </c>
+      <c r="B357" s="5" t="s">
+        <v>732</v>
+      </c>
+      <c r="C357" s="2" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="358" spans="1:5" ht="18" customHeight="1">
+      <c r="A358" s="5" t="s">
+        <v>719</v>
+      </c>
+      <c r="B358" s="5" t="s">
+        <v>733</v>
+      </c>
+      <c r="C358" s="2" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="359" spans="1:5" ht="18" customHeight="1">
+      <c r="A359" s="5" t="s">
+        <v>720</v>
+      </c>
+      <c r="B359" s="5" t="s">
+        <v>734</v>
+      </c>
+      <c r="C359" s="2" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="360" spans="1:5" ht="18" customHeight="1">
+      <c r="A360" s="5" t="s">
+        <v>721</v>
+      </c>
+      <c r="B360" s="5" t="s">
+        <v>735</v>
+      </c>
+      <c r="C360" s="2" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="361" spans="1:5" ht="18" customHeight="1">
+      <c r="A361" s="5" t="s">
+        <v>722</v>
+      </c>
+      <c r="B361" s="5" t="s">
+        <v>736</v>
+      </c>
+      <c r="C361" s="2" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="362" spans="1:5" ht="18" customHeight="1">
+      <c r="A362" s="5" t="s">
+        <v>723</v>
+      </c>
+      <c r="B362" s="5" t="s">
+        <v>737</v>
+      </c>
+      <c r="C362" s="2" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="363" spans="1:5" ht="18" customHeight="1">
+      <c r="A363" s="5" t="s">
+        <v>724</v>
+      </c>
+      <c r="B363" s="5" t="s">
+        <v>738</v>
+      </c>
+      <c r="C363" s="2" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="364" spans="1:5" ht="18" customHeight="1">
+      <c r="A364" s="5" t="s">
+        <v>725</v>
+      </c>
+      <c r="B364" s="5" t="s">
+        <v>739</v>
+      </c>
+      <c r="C364" s="2" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="365" spans="1:5" ht="18" customHeight="1">
+      <c r="A365"/>
+      <c r="B365"/>
+      <c r="C365"/>
+      <c r="D365"/>
+      <c r="E365"/>
+    </row>
+    <row r="366" spans="1:5" ht="18" customHeight="1">
+      <c r="A366"/>
+      <c r="B366"/>
+      <c r="C366"/>
+      <c r="D366"/>
+      <c r="E366"/>
+    </row>
+    <row r="367" spans="1:5" ht="18" customHeight="1">
+      <c r="A367"/>
+      <c r="B367"/>
+      <c r="C367"/>
+      <c r="D367"/>
+      <c r="E367"/>
+    </row>
+    <row r="368" spans="1:5" ht="18" customHeight="1">
+      <c r="A368"/>
+      <c r="B368"/>
+      <c r="C368"/>
+      <c r="D368"/>
+      <c r="E368"/>
+    </row>
+    <row r="369" spans="1:5" ht="18" customHeight="1">
+      <c r="A369"/>
+      <c r="B369"/>
+      <c r="C369"/>
+      <c r="D369"/>
+      <c r="E369"/>
+    </row>
+    <row r="370" spans="1:5" ht="18" customHeight="1">
+      <c r="A370"/>
+      <c r="B370"/>
+      <c r="C370"/>
+      <c r="D370"/>
+      <c r="E370"/>
+    </row>
+    <row r="371" spans="1:5" ht="18" customHeight="1">
+      <c r="A371"/>
+      <c r="B371"/>
+      <c r="C371"/>
+      <c r="D371"/>
+      <c r="E371"/>
+    </row>
+    <row r="372" spans="1:5" ht="18" customHeight="1">
+      <c r="A372"/>
+      <c r="B372"/>
+      <c r="C372"/>
+      <c r="D372"/>
+      <c r="E372"/>
+    </row>
+    <row r="373" spans="1:5" ht="18" customHeight="1">
+      <c r="A373"/>
+      <c r="B373"/>
+      <c r="C373"/>
+      <c r="D373"/>
+      <c r="E373"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/restaurant_crawler/list/總表.xlsx
+++ b/restaurant_crawler/list/總表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\slow3\OneDrive\桌面\GitHubProjects\BYOB\restaurant_crawler\list\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{476AEC7E-633F-4189-B565-157ABEEF89F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D49E1E71-F9DD-4ACB-8ECF-58A447C75198}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{E8354C52-640D-495B-A68D-B024E43CC161}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1110" uniqueCount="741">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1155" uniqueCount="771">
   <si>
     <t>name</t>
   </si>
@@ -2277,6 +2277,97 @@
   </si>
   <si>
     <t>火鍋 羊肉爐 薑母鴨</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>鳥萬炭火燒</t>
+  </si>
+  <si>
+    <t>串燒殿 敦南本店-東區串燒|串燒吃到飽|深夜串燒|聚餐推薦|聚餐餐廳|串燒推薦|居酒屋推薦|串燒店</t>
+  </si>
+  <si>
+    <t>品都串燒攤 忠孝</t>
+  </si>
+  <si>
+    <t>UNCLE RAY 串燒·牛飲·咖喱 台北大安</t>
+  </si>
+  <si>
+    <t>一期一會串燒</t>
+  </si>
+  <si>
+    <t>柒息地串燒居酒屋三重自強店</t>
+  </si>
+  <si>
+    <t>坂上源炭火酒場</t>
+  </si>
+  <si>
+    <t>吳留手串燒居酒屋 市民店</t>
+  </si>
+  <si>
+    <t>隆次郎燒鳥.串燒</t>
+  </si>
+  <si>
+    <t>GUGU Yakitori 居酒屋</t>
+  </si>
+  <si>
+    <t>七転八起-中山必吃串燒|人氣串燒|串燒專門店|串燒烤肉|熱門居酒屋|居酒屋推薦|喝酒聚餐推薦|隱藏居酒屋</t>
+  </si>
+  <si>
+    <t>庸人串燒 吉林店 Yong Ren Yakitori｜中山日式串燒居酒屋推薦｜台北深夜美食餐廳酒吧</t>
+  </si>
+  <si>
+    <t>獨領楓燒 （無油炸平價串烤）-中山平價碳烤|人氣串燒|平價串烤|CP串燒|熱門串烤|深夜串燒|串燒首選|在地推薦串燒</t>
+  </si>
+  <si>
+    <t>鳳 串燒酒居 | 燒鳥 | 居酒屋-中山/民權西路站日式居酒屋|特色居酒屋|必去居酒屋|推薦串燒|居酒屋推薦|人氣串燒|必吃串燒|日式碳烤串燒</t>
+  </si>
+  <si>
+    <t>yakitori_one@yummy-life.com</t>
+  </si>
+  <si>
+    <t>skewerapalace@gmail.com</t>
+  </si>
+  <si>
+    <t>willywillylai@gmail.com</t>
+  </si>
+  <si>
+    <t>uncleray1688@gmail.com</t>
+  </si>
+  <si>
+    <t>c183baa23371454f99f417f6616b724d@sentry.wixpress.com</t>
+  </si>
+  <si>
+    <t>ichimeet@gmail.com</t>
+  </si>
+  <si>
+    <t>qixidisanchong@gmail.com</t>
+  </si>
+  <si>
+    <t>saka0970586368@gmail.com</t>
+  </si>
+  <si>
+    <t>wuliushou@gmail.com</t>
+  </si>
+  <si>
+    <t>wang062787@gmail.com</t>
+  </si>
+  <si>
+    <t>partner@mctw.com.tw</t>
+  </si>
+  <si>
+    <t>daruma1044451@gmail.com</t>
+  </si>
+  <si>
+    <t>yong.ren.yakitori2@gmail.com</t>
+  </si>
+  <si>
+    <t>lonloveaym@hotmail.com</t>
+  </si>
+  <si>
+    <t>fong00560317@gmail.com</t>
+  </si>
+  <si>
+    <t>串燒</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2724,7 +2815,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDC20CA0-404E-4459-AB09-3585D9067841}">
-  <dimension ref="A1:H373"/>
+  <dimension ref="A1:H388"/>
   <sheetFormatPr defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="43.77734375" style="2" customWidth="1"/>
@@ -7177,67 +7268,240 @@
       </c>
     </row>
     <row r="365" spans="1:5" ht="18" customHeight="1">
-      <c r="A365"/>
-      <c r="B365"/>
-      <c r="C365"/>
+      <c r="A365" s="5" t="s">
+        <v>741</v>
+      </c>
+      <c r="B365" s="5" t="s">
+        <v>755</v>
+      </c>
+      <c r="C365" s="2" t="s">
+        <v>770</v>
+      </c>
       <c r="D365"/>
       <c r="E365"/>
     </row>
     <row r="366" spans="1:5" ht="18" customHeight="1">
-      <c r="A366"/>
-      <c r="B366"/>
-      <c r="C366"/>
+      <c r="A366" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="B366" s="5" t="s">
+        <v>756</v>
+      </c>
+      <c r="C366" s="2" t="s">
+        <v>770</v>
+      </c>
       <c r="D366"/>
       <c r="E366"/>
     </row>
     <row r="367" spans="1:5" ht="18" customHeight="1">
-      <c r="A367"/>
-      <c r="B367"/>
-      <c r="C367"/>
+      <c r="A367" s="5" t="s">
+        <v>743</v>
+      </c>
+      <c r="B367" s="5" t="s">
+        <v>757</v>
+      </c>
+      <c r="C367" s="2" t="s">
+        <v>770</v>
+      </c>
       <c r="D367"/>
       <c r="E367"/>
     </row>
     <row r="368" spans="1:5" ht="18" customHeight="1">
-      <c r="A368"/>
-      <c r="B368"/>
-      <c r="C368"/>
+      <c r="A368" s="5" t="s">
+        <v>744</v>
+      </c>
+      <c r="B368" s="5" t="s">
+        <v>758</v>
+      </c>
+      <c r="C368" s="2" t="s">
+        <v>770</v>
+      </c>
       <c r="D368"/>
       <c r="E368"/>
     </row>
     <row r="369" spans="1:5" ht="18" customHeight="1">
-      <c r="A369"/>
-      <c r="B369"/>
-      <c r="C369"/>
-      <c r="D369"/>
-      <c r="E369"/>
+      <c r="A369" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B369" s="5" t="s">
+        <v>759</v>
+      </c>
+      <c r="C369" s="2" t="s">
+        <v>770</v>
+      </c>
     </row>
     <row r="370" spans="1:5" ht="18" customHeight="1">
-      <c r="A370"/>
-      <c r="B370"/>
-      <c r="C370"/>
-      <c r="D370"/>
-      <c r="E370"/>
+      <c r="A370" s="5" t="s">
+        <v>745</v>
+      </c>
+      <c r="B370" s="5" t="s">
+        <v>760</v>
+      </c>
+      <c r="C370" s="2" t="s">
+        <v>770</v>
+      </c>
     </row>
     <row r="371" spans="1:5" ht="18" customHeight="1">
-      <c r="A371"/>
-      <c r="B371"/>
-      <c r="C371"/>
-      <c r="D371"/>
-      <c r="E371"/>
+      <c r="A371" s="5" t="s">
+        <v>746</v>
+      </c>
+      <c r="B371" s="5" t="s">
+        <v>761</v>
+      </c>
+      <c r="C371" s="2" t="s">
+        <v>770</v>
+      </c>
     </row>
     <row r="372" spans="1:5" ht="18" customHeight="1">
-      <c r="A372"/>
-      <c r="B372"/>
-      <c r="C372"/>
-      <c r="D372"/>
-      <c r="E372"/>
+      <c r="A372" s="5" t="s">
+        <v>747</v>
+      </c>
+      <c r="B372" s="5" t="s">
+        <v>762</v>
+      </c>
+      <c r="C372" s="2" t="s">
+        <v>770</v>
+      </c>
     </row>
     <row r="373" spans="1:5" ht="18" customHeight="1">
-      <c r="A373"/>
-      <c r="B373"/>
-      <c r="C373"/>
-      <c r="D373"/>
-      <c r="E373"/>
+      <c r="A373" s="5" t="s">
+        <v>748</v>
+      </c>
+      <c r="B373" s="5" t="s">
+        <v>763</v>
+      </c>
+      <c r="C373" s="2" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="374" spans="1:5" ht="18" customHeight="1">
+      <c r="A374" s="5" t="s">
+        <v>749</v>
+      </c>
+      <c r="B374" s="5" t="s">
+        <v>764</v>
+      </c>
+      <c r="C374" s="2" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="375" spans="1:5" ht="18" customHeight="1">
+      <c r="A375" s="5" t="s">
+        <v>750</v>
+      </c>
+      <c r="B375" s="5" t="s">
+        <v>765</v>
+      </c>
+      <c r="C375" s="2" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="376" spans="1:5" ht="18" customHeight="1">
+      <c r="A376" s="5" t="s">
+        <v>751</v>
+      </c>
+      <c r="B376" s="5" t="s">
+        <v>766</v>
+      </c>
+      <c r="C376" s="2" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="377" spans="1:5" ht="18" customHeight="1">
+      <c r="A377" s="5" t="s">
+        <v>752</v>
+      </c>
+      <c r="B377" s="5" t="s">
+        <v>767</v>
+      </c>
+      <c r="C377" s="2" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="378" spans="1:5" ht="18" customHeight="1">
+      <c r="A378" s="5" t="s">
+        <v>753</v>
+      </c>
+      <c r="B378" s="5" t="s">
+        <v>768</v>
+      </c>
+      <c r="C378" s="2" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="379" spans="1:5" ht="18" customHeight="1">
+      <c r="A379" s="5" t="s">
+        <v>754</v>
+      </c>
+      <c r="B379" s="5" t="s">
+        <v>769</v>
+      </c>
+      <c r="C379" s="2" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="380" spans="1:5" ht="18" customHeight="1">
+      <c r="A380"/>
+      <c r="B380"/>
+      <c r="C380"/>
+      <c r="D380"/>
+      <c r="E380"/>
+    </row>
+    <row r="381" spans="1:5" ht="18" customHeight="1">
+      <c r="A381"/>
+      <c r="B381"/>
+      <c r="C381"/>
+      <c r="D381"/>
+      <c r="E381"/>
+    </row>
+    <row r="382" spans="1:5" ht="18" customHeight="1">
+      <c r="A382"/>
+      <c r="B382"/>
+      <c r="C382"/>
+      <c r="D382"/>
+      <c r="E382"/>
+    </row>
+    <row r="383" spans="1:5" ht="18" customHeight="1">
+      <c r="A383"/>
+      <c r="B383"/>
+      <c r="C383"/>
+      <c r="D383"/>
+      <c r="E383"/>
+    </row>
+    <row r="384" spans="1:5" ht="18" customHeight="1">
+      <c r="A384"/>
+      <c r="B384"/>
+      <c r="C384"/>
+      <c r="D384"/>
+      <c r="E384"/>
+    </row>
+    <row r="385" spans="1:5" ht="18" customHeight="1">
+      <c r="A385"/>
+      <c r="B385"/>
+      <c r="C385"/>
+      <c r="D385"/>
+      <c r="E385"/>
+    </row>
+    <row r="386" spans="1:5" ht="18" customHeight="1">
+      <c r="A386"/>
+      <c r="B386"/>
+      <c r="C386"/>
+      <c r="D386"/>
+      <c r="E386"/>
+    </row>
+    <row r="387" spans="1:5" ht="18" customHeight="1">
+      <c r="A387"/>
+      <c r="B387"/>
+      <c r="C387"/>
+      <c r="D387"/>
+      <c r="E387"/>
+    </row>
+    <row r="388" spans="1:5" ht="18" customHeight="1">
+      <c r="A388"/>
+      <c r="B388"/>
+      <c r="C388"/>
+      <c r="D388"/>
+      <c r="E388"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -7247,5 +7511,6 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
 </worksheet>
 </file>